--- a/data/trending_integrated_20260911_10.xlsx
+++ b/data/trending_integrated_20260911_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15890</v>
+        <v>15190</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+31.43%</t>
+          <t>+22.90%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.11</v>
+        <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>229</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>602</v>
+        <v>62</v>
       </c>
       <c r="H2" t="n">
-        <v>3.14</v>
+        <v>2.39</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12090</v>
+        <v>12360</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>15270</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>12690</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03</v>
+        <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>138864000000</v>
+        <v>133015683445</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="R2" t="n">
-        <v>-268000</v>
+        <v>-139000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 유가 폭등으로 인한 급등 기대감. WTI 100달러 돌파 및 3연상 목표.</t>
+          <t>젠슨 황의 AI 사이버 보안 시장 지목으로 인한 양자 보안 테마 부각. 보안 섹터 급등 및 특징주 기대감 고조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['유가 폭등', '중동 전쟁', '3연상']</t>
+          <t>['엑스게이트', '사이버 보안', '젠슨 황']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138900</v>
+        <v>136500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+20.05%</t>
+          <t>+17.98%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="H3" t="n">
         <v>4.32</v>
@@ -702,7 +702,7 @@
         <v>4.58</v>
       </c>
       <c r="O3" t="n">
-        <v>324176395200</v>
+        <v>340623003250</v>
       </c>
       <c r="P3" t="n">
         <v>196800</v>
@@ -711,14 +711,14 @@
         <v>27750</v>
       </c>
       <c r="R3" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>애플 및 무라타 관련 추정 속에서 삼화콘덴서의 급등세. 일회성 호재 가능성 및 고점 당김 논란.</t>
+          <t>애플 및 무라타 관련 일회성 호재로 인한 급등 가능성 언급. 손바뀜 및 고점 우려 공존.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['애플', '무라타']</t>
+          <t>['삼화콘덴서', '애플', '무라타']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14660</v>
+        <v>8300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+16.26%</t>
+          <t>+11.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.22</v>
+        <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>42</v>
+        <v>535</v>
       </c>
       <c r="H4" t="n">
-        <v>2.39</v>
+        <v>1.29</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12610</v>
+        <v>7420</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.61</v>
+        <v>1.17</v>
       </c>
       <c r="O4" t="n">
-        <v>101860000000</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -803,27 +803,27 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-107000</v>
+        <v>20000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>젠슨 황의 AI 사이버 보안 발언에 따른 엑스게이트의 양자 보안 테마 급등. 보안 섹터 내 대장주로서의 부각.</t>
+          <t>중요 임상 데이터 발표(9월 14일) 및 기술 수출 가능성에 대한 기대감. 제약·바이오 섹터 전반의 강세 속에서 주목.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자보안', '젠슨 황']</t>
+          <t>['임상', '데이터', '기술수출']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,46 +832,46 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8300</v>
+        <v>1955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+11.08%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="E5" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>523</v>
+        <v>108</v>
       </c>
       <c r="H5" t="n">
-        <v>1.29</v>
+        <v>2.44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7420</v>
+        <v>1760</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.17</v>
+        <v>2.12</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>30668000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -895,27 +895,27 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>16000</v>
+        <v>-1017000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>임상 시험 디자인 공개 및 14일 예정된 데이터 발표에 대한 기대감.</t>
+          <t>국제 유가 상승 및 전쟁 테마주 부각으로 인한 급등 가능성 언급. 보유 물량 매도 및 매수 의견 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['임상 시험', '데이터 발표', '기술 수출']</t>
+          <t>['전쟁 테마주', '국제 유가', '흥아해운']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28950</v>
+        <v>15800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+10.92%</t>
+          <t>+8.89%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.01</v>
+        <v>3.11</v>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>243</v>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="G6" t="n">
-        <v>209</v>
+        <v>620</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32</v>
+        <v>3.14</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>26100</v>
+        <v>14510</v>
       </c>
       <c r="K6" t="n">
-        <v>26350</v>
+        <v>17010</v>
       </c>
       <c r="L6" t="n">
-        <v>30300</v>
+        <v>17310</v>
       </c>
       <c r="M6" t="n">
-        <v>25400</v>
+        <v>15600</v>
       </c>
       <c r="N6" t="n">
-        <v>0.33</v>
+        <v>0.03</v>
       </c>
       <c r="O6" t="n">
-        <v>211761576400</v>
+        <v>143284545720</v>
       </c>
       <c r="P6" t="n">
-        <v>39350</v>
+        <v>36200</v>
       </c>
       <c r="Q6" t="n">
-        <v>8200</v>
+        <v>8920</v>
       </c>
       <c r="R6" t="n">
-        <v>12000</v>
+        <v>-347000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>신규 상장주로서 스카이랩스의 급등세. 조정 후 수급 개선 및 추가 상승 기대감 표출.</t>
+          <t>중동 전쟁 및 국제 유가 폭등으로 인한 3연상 기대감. WTI 100달러 돌파 및 추가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['신규주', '수급']</t>
+          <t>['흥구석유', '국제 유가', '중동 전쟁']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7680</v>
+        <v>53200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+2.70%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>-0.44</v>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>196</v>
+        <v>63</v>
       </c>
       <c r="H7" t="n">
-        <v>11.72</v>
+        <v>2.92</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7100</v>
+        <v>51800</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>51300</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>53800</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>51300</v>
       </c>
       <c r="N7" t="n">
-        <v>11.62</v>
+        <v>3.36</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>46305124300</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>87700</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>17210</v>
       </c>
       <c r="R7" t="n">
-        <v>150000</v>
+        <v>-14000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>기관 및 외국인 매매 단가 분석과 저점 매수 기회 언급.</t>
+          <t>미국 태양광 흐름 및 SK의 자본력 콜라보를 통한 상방 추세 기대. 개미 매도세에 대한 우려 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관 매매', '저점 매수']</t>
+          <t>['SK이터닉스', '태양광', 'SK']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9980</v>
+        <v>414500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.54%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="H8" t="n">
-        <v>4.49</v>
+        <v>38.02</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9280</v>
+        <v>415500</v>
       </c>
       <c r="K8" t="n">
-        <v>10030</v>
+        <v>407000</v>
       </c>
       <c r="L8" t="n">
-        <v>10880</v>
+        <v>415500</v>
       </c>
       <c r="M8" t="n">
-        <v>9800</v>
+        <v>404000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.42</v>
+        <v>37.82</v>
       </c>
       <c r="O8" t="n">
-        <v>17725269150</v>
+        <v>24610561750</v>
       </c>
       <c r="P8" t="n">
-        <v>15640</v>
+        <v>822000</v>
       </c>
       <c r="Q8" t="n">
-        <v>5470</v>
+        <v>283000</v>
       </c>
       <c r="R8" t="n">
-        <v>-6000</v>
+        <v>5000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>프리갈리앙 베스트 의료기술상 수상 소식과 거래량 증가 언급.</t>
+          <t>로봇 관절 부품 수주 및 미래차·로봇 신기술 공개 등 구체적인 호재 언급. 저평가 및 유럽 중국차 관세 관련 반사이익 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수상', '의료기술', '거래량']</t>
+          <t>['로봇', '수주', '미래차']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1952</v>
+        <v>50000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.32</v>
+        <v>0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="G9" t="n">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="H9" t="n">
-        <v>2.44</v>
+        <v>38.78</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1901</v>
+        <v>50400</v>
       </c>
       <c r="K9" t="n">
-        <v>2050</v>
+        <v>50500</v>
       </c>
       <c r="L9" t="n">
-        <v>2080</v>
+        <v>50600</v>
       </c>
       <c r="M9" t="n">
-        <v>1950</v>
+        <v>49650</v>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>38.69</v>
       </c>
       <c r="O9" t="n">
-        <v>30075511103</v>
+        <v>31371068750</v>
       </c>
       <c r="P9" t="n">
-        <v>4795</v>
+        <v>67300</v>
       </c>
       <c r="Q9" t="n">
-        <v>1524</v>
+        <v>23150</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-110000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국제 유가 상승에 따른 전쟁 테마주로서의 흥아해운 및 장금상선 관련 언급. 일부 외인 매도세 포착.</t>
+          <t>약 4.7조 원 규모의 대규모 수주 공시 확인. 사우디, 베트남 등 겹호재와 외국인 매수세 언급. 긍정적 추세 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['국제유가', '전쟁테마주']</t>
+          <t>['수주', '공시', '외국인']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90200</v>
+        <v>19500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="F10" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>667</v>
+        <v>282</v>
       </c>
       <c r="H10" t="n">
-        <v>23.59</v>
+        <v>10.65</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>89900</v>
+        <v>19750</v>
       </c>
       <c r="K10" t="n">
-        <v>88700</v>
+        <v>19500</v>
       </c>
       <c r="L10" t="n">
-        <v>90400</v>
+        <v>19840</v>
       </c>
       <c r="M10" t="n">
-        <v>88000</v>
+        <v>19060</v>
       </c>
       <c r="N10" t="n">
-        <v>23.65</v>
+        <v>10.64</v>
       </c>
       <c r="O10" t="n">
-        <v>68172775800</v>
+        <v>54223301025</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-126000</v>
+        <v>-249000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>에너지 대미 투자 협상 마무리 소식과 29.7조 수주잔고 언급.</t>
+          <t>NH투자증권의 목표주가 상향 조정 및 대차해지 운동 동참 독려. 신규 투자자 대상 대차해지 강조.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['투자 협상', '수주잔고', '원전']</t>
+          <t>['대우건설', 'NH투자증권', '대차해지']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50200</v>
+        <v>14740</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.09</v>
+        <v>-0.39</v>
       </c>
       <c r="E11" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>388</v>
+        <v>136</v>
       </c>
       <c r="H11" t="n">
-        <v>38.78</v>
+        <v>2.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>50400</v>
+        <v>14960</v>
       </c>
       <c r="K11" t="n">
-        <v>50500</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>50600</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>49650</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>38.69</v>
+        <v>2.89</v>
       </c>
       <c r="O11" t="n">
-        <v>30220923575</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>67300</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>23150</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-54000</v>
+        <v>-34000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 계약 체결 공시 확인. 사우디, 베트남 관련 호재 언급.</t>
+          <t>외국인 매수세 유입 및 상승 가능성에 대한 기대감. 단기적인 매매 기회 언급도 있으나, 뚜렷한 성장 전망 근거는 부족.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['계약', '공시', '수주']</t>
+          <t>['외국인', '매수', '단기매매']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>415500</v>
+        <v>89900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="G12" t="n">
-        <v>165</v>
+        <v>688</v>
       </c>
       <c r="H12" t="n">
-        <v>38.02</v>
+        <v>23.59</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>417500</v>
+        <v>91700</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>37.82</v>
+        <v>23.65</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1539,27 +1539,27 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4000</v>
+        <v>-245000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>차부품 넘어 로봇 사업 확장 및 유럽 중국차 관세 관련 호재. 아틀라스 관절부품 수주 및 글로벌 수주전 기대.</t>
+          <t>대규모 수주 및 미국 투자 협상 마무리 등 긍정적인 뉴스 언급. 원전 관련 수급 집중 및 수주잔고 증가에 따른 상승 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['현대모비스', '로봇', '수주']</t>
+          <t>['원전', '수주', '수주잔고']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19620</v>
+        <v>192300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>269</v>
+        <v>41</v>
       </c>
       <c r="H13" t="n">
-        <v>10.65</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>19750</v>
+        <v>197500</v>
       </c>
       <c r="K13" t="n">
-        <v>19500</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>19840</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>19060</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>10.64</v>
+        <v>75.92</v>
       </c>
       <c r="O13" t="n">
-        <v>51323366020</v>
+        <v>241373000000</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-18000</v>
+        <v>-405000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-52000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>NH투자증권의 목표주가 상향 조정 및 대차해지 참여 독려. 신규 및 기존 주주들의 주주 행동 촉구.</t>
+          <t>미국 증시 폭락 영향으로 인한 하락세 지속 전망. 우선주의 든든한 피난처 역할 기대와 함께 부정적 의견 우세.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대차해지', '목표주가 상향']</t>
+          <t>['삼성전자우', '미국 증시', '하락 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14205</v>
+        <v>14150</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.11</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G14" t="n">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="H14" t="n">
         <v>5.98</v>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14320</v>
+        <v>14600</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>14800</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>14950</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>14020</v>
       </c>
       <c r="N14" t="n">
         <v>6.09</v>
       </c>
       <c r="O14" t="n">
-        <v>56621000000</v>
+        <v>60248836165</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>30200</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3540</v>
       </c>
       <c r="R14" t="n">
-        <v>-174000</v>
+        <v>-297000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-61000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>자포리 원전 관련 모멘텀 및 원전주 강세 속 우리기술의 급등 가능성 언급. 단기 과열 및 조정 가능성도 제기.</t>
+          <t>원전 관련 모멘텀에 대한 기대감과 함께 단기적인 조정 후 상승 가능성 언급. 일부 부정적 전망도 혼재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '자포리']</t>
+          <t>['원전', '120일선', '단기과열']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,60 +1759,60 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14740</v>
+        <v>7430</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-3.26%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.39</v>
+        <v>0.1</v>
       </c>
       <c r="E15" t="n">
+        <v>76</v>
+      </c>
+      <c r="F15" t="n">
         <v>44</v>
       </c>
-      <c r="F15" t="n">
-        <v>25</v>
-      </c>
       <c r="G15" t="n">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5</v>
+        <v>11.72</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14960</v>
+        <v>7680</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>7540</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>7660</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="N15" t="n">
-        <v>2.89</v>
+        <v>11.62</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5932820035</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>8850</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4220</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 언급 및 5일선, 20일선 지지 기반 매수 전략.</t>
+          <t>기관 및 외국인 매매 단가 분석과 저점 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['외국인 매수', '분할 매수']</t>
+          <t>['기관 매매', '저점 매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>260000</v>
+        <v>15120</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>-3.32%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
-        <v>510</v>
+        <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>2260</v>
+        <v>138</v>
       </c>
       <c r="H16" t="n">
-        <v>46.71</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>269000</v>
+        <v>15640</v>
       </c>
       <c r="K16" t="n">
-        <v>258000</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>261000</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>257500</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>46.81</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>846658589250</v>
+        <v>12418000000</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>72100</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-396000</v>
+        <v>23000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>FOMC 및 거시 경제 요인에 따른 삼성전자 주가 하락 전망과 일부 반등 기대 혼재. 게시판 분위기 변화 언급.</t>
+          <t>호남 반도체 부지 확보 및 메가 건설 관련 긍정적 전망. 친환경 특화 기업 투자 및 상승 추세 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['FOMC', '거시경제']</t>
+          <t>['금호건설', '반도체', '메가 건설']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1787000</v>
+        <v>259500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.72%</t>
+          <t>-3.71%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" t="n">
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>464</v>
+        <v>501</v>
       </c>
       <c r="G17" t="n">
-        <v>1386</v>
+        <v>2214</v>
       </c>
       <c r="H17" t="n">
-        <v>50.55</v>
+        <v>46.71</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1856000</v>
+        <v>269500</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>50.67</v>
+        <v>46.81</v>
       </c>
       <c r="O17" t="n">
-        <v>1408153000000</v>
+        <v>892163000000</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1999,27 +1999,27 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-115000</v>
+        <v>-615000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-530000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>오라클 실적 호조 및 AI 클라우드 수요 증가에도 불구하고 SK하이닉스 주가 하락세. 트럼프 관련 정치적 이슈 언급.</t>
+          <t>매크로 및 FOMC 영향으로 인한 하락 전망과 JP모건의 저평가 분석 및 투자 의견 상향 언급. 게시판 분위기 혼조.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI', '오라클 실적']</t>
+          <t>['삼성전자', '매크로', 'JP모건']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>192800</v>
+        <v>1783000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.02%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="E18" t="n">
-        <v>44</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>34</v>
+        <v>462</v>
       </c>
       <c r="G18" t="n">
-        <v>38</v>
+        <v>1339</v>
       </c>
       <c r="H18" t="n">
-        <v>75.98999999999999</v>
+        <v>50.55</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>203000</v>
+        <v>1856000</v>
       </c>
       <c r="K18" t="n">
-        <v>195000</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>195600</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>192500</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>75.92</v>
+        <v>50.67</v>
       </c>
       <c r="O18" t="n">
-        <v>218119704050</v>
+        <v>1506224000000</v>
       </c>
       <c r="P18" t="n">
-        <v>243500</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-196000</v>
+        <v>-166000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-111000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 증시 폭락에 따른 삼성전자우 주가 하락 및 피난처로서의 역할 기대. 외인 수급 및 주가 변동성에 대한 부정적 언급.</t>
+          <t>AI 클라우드 수요 폭발 관련 오라클 실적 발표에도 불구하고 하락세 지속. 저점 매수 및 분할 매수 전략 고려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['우선주', '미국증시']</t>
+          <t>['SK하이닉스', 'AI', '오라클']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12210</v>
+        <v>28750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.29%</t>
+          <t>-5.12%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>42</v>
+        <v>144</v>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="G19" t="n">
-        <v>54</v>
+        <v>229</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>13030</v>
+        <v>30300</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2171,10 +2171,10 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="O19" t="n">
-        <v>29705000000</v>
+        <v>223240000000</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2183,14 +2183,14 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>원전 테마 내 삼미금속을 대장주로 언급하며 타 원전주(한전기술, TCC스틸) 급등세 관찰. 지수 부진 및 거래량 부족 지적.</t>
+          <t>개인 투자자들의 긍정적 기대감이 높은 가운데, 단기적인 수급 개선 및 신규주로서의 잠재력에 대한 언급. 그러나 구체적인 근거 제시 미흡.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '삼미금속']</t>
+          <t>['수급', '신규주']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>233500</v>
+        <v>9280</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-7.71%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="F20" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>459</v>
+        <v>204</v>
       </c>
       <c r="H20" t="n">
-        <v>7.58</v>
+        <v>4.49</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>253000</v>
+        <v>9800</v>
       </c>
       <c r="K20" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>8.539999999999999</v>
+        <v>4.42</v>
       </c>
       <c r="O20" t="n">
-        <v>110041782750</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>426000</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-41000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>곽동신 관련 발언과 기관 매수 언급. HBM 관련 논의.</t>
+          <t>수상 소식 언급에도 불구하고 주가 하락 및 거래량 증가에 대한 의구심 표출. 실질적인 호재나 뉴스 부재 속 관망세.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,18 +2291,202 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['기관 매수', 'HBM']</t>
+          <t>['수상', '거래량', '호재']</t>
         </is>
       </c>
       <c r="X20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>064550</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>12080</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-7.29%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G21" t="n">
+        <v>54</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>13030</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="O21" t="n">
+        <v>30853000000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-94000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>원전 테마 내 다른 종목(한전기술, TCC스틸)의 강세 속에서 삼미금속의 상대적 부진 및 거래량 부족에 대한 언급. 일부 매수 기회 언급.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['원전', '테마', '거래량']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>012210</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>233500</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-7.71%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="E22" t="n">
+        <v>140</v>
+      </c>
+      <c r="F22" t="n">
+        <v>76</v>
+      </c>
+      <c r="G22" t="n">
+        <v>484</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>253000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>241000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>241000</v>
+      </c>
+      <c r="M22" t="n">
+        <v>231000</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="O22" t="n">
+        <v>115476938000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>426000</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>86100</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-224000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-14000</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>주가 하락 및 공매도에 대한 불만 표출. 회사 차원의 자사주 매입 소각, 무증 발표 요구. 긍정적인 뉴스나 근거는 부족.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['공매도', '자사주', '매수']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
         <v>1</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>042700</t>
         </is>

--- a/data/trending_integrated_20260911_10.xlsx
+++ b/data/trending_integrated_20260911_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15190</v>
+        <v>15650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+22.90%</t>
+          <t>+29.45%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.22</v>
+        <v>3.11</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>262</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="G2" t="n">
-        <v>62</v>
+        <v>668</v>
       </c>
       <c r="H2" t="n">
-        <v>2.39</v>
+        <v>3.14</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12360</v>
+        <v>12090</v>
       </c>
       <c r="K2" t="n">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>15270</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>12690</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.61</v>
+        <v>0.03</v>
       </c>
       <c r="O2" t="n">
-        <v>133015683445</v>
+        <v>147556000000</v>
       </c>
       <c r="P2" t="n">
-        <v>30550</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-139000</v>
+        <v>-347000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>젠슨 황의 AI 사이버 보안 시장 지목으로 인한 양자 보안 테마 부각. 보안 섹터 급등 및 특징주 기대감 고조.</t>
+          <t>중동 전쟁 및 국제 유가 폭등으로 인한 3연상 기대감. WTI 100달러 돌파 및 추가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['엑스게이트', '사이버 보안', '젠슨 황']</t>
+          <t>['흥구석유', '국제 유가', '중동 전쟁']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,86 +648,86 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>136500</v>
+        <v>15150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+17.98%</t>
+          <t>+22.57%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.26</v>
+        <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="H3" t="n">
-        <v>4.32</v>
+        <v>2.39</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>115700</v>
+        <v>12360</v>
       </c>
       <c r="K3" t="n">
-        <v>112100</v>
+        <v>12800</v>
       </c>
       <c r="L3" t="n">
-        <v>147500</v>
+        <v>15380</v>
       </c>
       <c r="M3" t="n">
-        <v>112000</v>
+        <v>12690</v>
       </c>
       <c r="N3" t="n">
-        <v>4.58</v>
+        <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>340623003250</v>
+        <v>152905425730</v>
       </c>
       <c r="P3" t="n">
-        <v>196800</v>
+        <v>30550</v>
       </c>
       <c r="Q3" t="n">
-        <v>27750</v>
+        <v>6100</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-139000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>애플 및 무라타 관련 일회성 호재로 인한 급등 가능성 언급. 손바뀜 및 고점 우려 공존.</t>
+          <t>PQC 암호모듈 KCMVP 인증 획득 및 미국 양자보안 시장 진출. 젠슨황 발언 관련 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['삼화콘덴서', '애플', '무라타']</t>
+          <t>['PQC', '양자보안', '젠슨황']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,46 +740,46 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8300</v>
+        <v>138400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+19.00%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="E4" t="n">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>535</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
-        <v>1.29</v>
+        <v>4.32</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7420</v>
+        <v>116300</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.17</v>
+        <v>4.58</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>353434000000</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -803,27 +803,27 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>20000</v>
+        <v>75000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>중요 임상 데이터 발표(9월 14일) 및 기술 수출 가능성에 대한 기대감. 제약·바이오 섹터 전반의 강세 속에서 주목.</t>
+          <t>애플 및 무라타 관련 기대감으로 인한 급등. 손바뀜 및 차트 분석.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['임상', '데이터', '기술수출']</t>
+          <t>['애플', '무라타', '손바뀜']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,46 +832,46 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1955</v>
+        <v>8300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+11.08%</t>
+          <t>+11.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>108</v>
+        <v>549</v>
       </c>
       <c r="H5" t="n">
-        <v>2.44</v>
+        <v>1.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1760</v>
+        <v>7420</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.12</v>
+        <v>1.17</v>
       </c>
       <c r="O5" t="n">
-        <v>30668000000</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -895,27 +895,27 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-1017000</v>
+        <v>20000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>국제 유가 상승 및 전쟁 테마주 부각으로 인한 급등 가능성 언급. 보유 물량 매도 및 매수 의견 혼재.</t>
+          <t>중요 임상 데이터 발표(9월 14일) 및 기술 수출 가능성에 대한 기대감. 제약·바이오 섹터 전반의 강세 속에서 주목.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', '국제 유가', '흥아해운']</t>
+          <t>['임상', '데이터', '기술수출']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15800</v>
+        <v>7680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+8.89%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.11</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
-        <v>152</v>
+        <v>47</v>
       </c>
       <c r="G6" t="n">
-        <v>620</v>
+        <v>231</v>
       </c>
       <c r="H6" t="n">
-        <v>3.14</v>
+        <v>11.72</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14510</v>
+        <v>7100</v>
       </c>
       <c r="K6" t="n">
-        <v>17010</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>17310</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03</v>
+        <v>11.62</v>
       </c>
       <c r="O6" t="n">
-        <v>143284545720</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>36200</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8920</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-347000</v>
+        <v>100000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 국제 유가 폭등으로 인한 3연상 기대감. WTI 100달러 돌파 및 추가 상승 가능성 언급.</t>
+          <t>외국인/기관 평균 매매단가 분석 결과 제시. 신영증권 출몰에 따른 개미들의 혼비백산 및 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['흥구석유', '국제 유가', '중동 전쟁']</t>
+          <t>['외국인/기관', '매매단가', '주가 조작']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53200</v>
+        <v>10000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+2.70%</t>
+          <t>+7.76%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.44</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>63</v>
+        <v>208</v>
       </c>
       <c r="H7" t="n">
-        <v>2.92</v>
+        <v>4.49</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>51800</v>
+        <v>9280</v>
       </c>
       <c r="K7" t="n">
-        <v>51300</v>
+        <v>10030</v>
       </c>
       <c r="L7" t="n">
-        <v>53800</v>
+        <v>10880</v>
       </c>
       <c r="M7" t="n">
-        <v>51300</v>
+        <v>9800</v>
       </c>
       <c r="N7" t="n">
-        <v>3.36</v>
+        <v>4.42</v>
       </c>
       <c r="O7" t="n">
-        <v>46305124300</v>
+        <v>18459975900</v>
       </c>
       <c r="P7" t="n">
-        <v>87700</v>
+        <v>15640</v>
       </c>
       <c r="Q7" t="n">
-        <v>17210</v>
+        <v>5470</v>
       </c>
       <c r="R7" t="n">
-        <v>-14000</v>
+        <v>-41000</v>
       </c>
       <c r="S7" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 태양광 흐름 및 SK의 자본력 콜라보를 통한 상방 추세 기대. 개미 매도세에 대한 우려 존재.</t>
+          <t>프리갈리앙 베스트 의료기술상 수상이라는 호재에도 불구하고 주가 하락. 공매도 세력과의 승부 및 역대급 거래량 기대감 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['SK이터닉스', '태양광', 'SK']</t>
+          <t>['프리갈리앙 수상', '의료 기술', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>414500</v>
+        <v>1938</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>180</v>
+        <v>112</v>
       </c>
       <c r="H8" t="n">
-        <v>38.02</v>
+        <v>2.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>415500</v>
+        <v>1901</v>
       </c>
       <c r="K8" t="n">
-        <v>407000</v>
+        <v>2050</v>
       </c>
       <c r="L8" t="n">
-        <v>415500</v>
+        <v>2080</v>
       </c>
       <c r="M8" t="n">
-        <v>404000</v>
+        <v>1933</v>
       </c>
       <c r="N8" t="n">
-        <v>37.82</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>24610561750</v>
+        <v>32314373114</v>
       </c>
       <c r="P8" t="n">
-        <v>822000</v>
+        <v>4795</v>
       </c>
       <c r="Q8" t="n">
-        <v>283000</v>
+        <v>1524</v>
       </c>
       <c r="R8" t="n">
-        <v>5000</v>
+        <v>-1017000</v>
       </c>
       <c r="S8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>로봇 관절 부품 수주 및 미래차·로봇 신기술 공개 등 구체적인 호재 언급. 저평가 및 유럽 중국차 관세 관련 반사이익 기대.</t>
+          <t>국제유가 상승 및 전쟁 테마 관련 기대감. 장금상선 보유 수량 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['로봇', '수주', '미래차']</t>
+          <t>['전쟁 테마', '국제유가', '장금상선']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50000</v>
+        <v>53400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.09</v>
+        <v>-0.44</v>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>402</v>
+        <v>70</v>
       </c>
       <c r="H9" t="n">
-        <v>38.78</v>
+        <v>2.92</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>50400</v>
+        <v>53200</v>
       </c>
       <c r="K9" t="n">
-        <v>50500</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50600</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>49650</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>38.69</v>
+        <v>3.36</v>
       </c>
       <c r="O9" t="n">
-        <v>31371068750</v>
+        <v>50042000000</v>
       </c>
       <c r="P9" t="n">
-        <v>67300</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>23150</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-110000</v>
+        <v>-14000</v>
       </c>
       <c r="S9" t="n">
-        <v>-4000</v>
+        <v>4000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>약 4.7조 원 규모의 대규모 수주 공시 확인. 사우디, 베트남 등 겹호재와 외국인 매수세 언급. 긍정적 추세 전망.</t>
+          <t>미국 태양광 섹터 흐름 양호 및 양자보안 테마 기대감. SK와 자본력 콜라보.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주', '공시', '외국인']</t>
+          <t>['태양광', '양자보안', 'SK']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19500</v>
+        <v>19470</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="H10" t="n">
         <v>10.65</v>
@@ -1331,28 +1331,28 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19750</v>
+        <v>19450</v>
       </c>
       <c r="K10" t="n">
-        <v>19500</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>19840</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>19060</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>10.64</v>
       </c>
       <c r="O10" t="n">
-        <v>54223301025</v>
+        <v>56975000000</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>-249000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NH투자증권의 목표주가 상향 조정 및 대차해지 운동 동참 독려. 신규 투자자 대상 대차해지 강조.</t>
+          <t>NH투자증권의 목표주가 상향 조정. 대차해지 운동 동참 촉구.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['대우건설', 'NH투자증권', '대차해지']</t>
+          <t>['NH투자증권', '목표주가', '대차해지']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,39 +1391,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14740</v>
+        <v>415500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.39</v>
+        <v>0.2</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5</v>
+        <v>38.02</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14960</v>
+        <v>417500</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.89</v>
+        <v>37.82</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1447,27 +1447,27 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-34000</v>
+        <v>5000</v>
       </c>
       <c r="S11" t="n">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 및 상승 가능성에 대한 기대감. 단기적인 매매 기회 언급도 있으나, 뚜렷한 성장 전망 근거는 부족.</t>
+          <t>로봇 관절 부품 수주 및 미래차·로봇 신기술 공개 등 구체적인 호재 언급. 저평가 및 유럽 중국차 관세 관련 반사이익 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['외국인', '매수', '단기매매']</t>
+          <t>['로봇', '수주', '미래차']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89900</v>
+        <v>49950</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="F12" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="G12" t="n">
-        <v>688</v>
+        <v>406</v>
       </c>
       <c r="H12" t="n">
-        <v>23.59</v>
+        <v>38.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>91700</v>
+        <v>50400</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>50500</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>50600</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>49650</v>
       </c>
       <c r="N12" t="n">
-        <v>23.65</v>
+        <v>38.69</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>33201786050</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>67300</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>23150</v>
       </c>
       <c r="R12" t="n">
-        <v>-245000</v>
+        <v>-110000</v>
       </c>
       <c r="S12" t="n">
-        <v>10000</v>
+        <v>-4000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대규모 수주 및 미국 투자 협상 마무리 등 긍정적인 뉴스 언급. 원전 관련 수급 집중 및 수주잔고 증가에 따른 상승 기대.</t>
+          <t>약 4.7조 원 규모의 대규모 수주 공시 확인. 사우디, 베트남 등 겹호재와 외국인 매수세 언급. 긍정적 추세 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '수주', '수주잔고']</t>
+          <t>['수주', '공시', '외국인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,46 +1568,46 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>192300</v>
+        <v>14120</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>41</v>
+        <v>374</v>
       </c>
       <c r="H13" t="n">
-        <v>75.98999999999999</v>
+        <v>5.98</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>197500</v>
+        <v>14320</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>75.92</v>
+        <v>6.09</v>
       </c>
       <c r="O13" t="n">
-        <v>241373000000</v>
+        <v>62497000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1631,27 +1631,27 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-405000</v>
+        <v>-297000</v>
       </c>
       <c r="S13" t="n">
-        <v>-52000</v>
+        <v>-61000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 영향으로 인한 하락세 지속 전망. 우선주의 든든한 피난처 역할 기대와 함께 부정적 의견 우세.</t>
+          <t>원전 관련 테마 기대감 속에서 모건 스탠리의 대량 매수 관측. 단기 과열 우려도 있으나, 원전주의 강력한 재료 기반 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['삼성전자우', '미국 증시', '하락 전망']</t>
+          <t>['원전 테마', '모건 스탠리', '수주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14150</v>
+        <v>14740</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.11</v>
+        <v>-0.39</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G14" t="n">
-        <v>359</v>
+        <v>141</v>
       </c>
       <c r="H14" t="n">
-        <v>5.98</v>
+        <v>2.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14600</v>
+        <v>14960</v>
       </c>
       <c r="K14" t="n">
-        <v>14800</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>14950</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>14020</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6.09</v>
+        <v>2.89</v>
       </c>
       <c r="O14" t="n">
-        <v>60248836165</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3540</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-297000</v>
+        <v>-34000</v>
       </c>
       <c r="S14" t="n">
-        <v>-61000</v>
+        <v>-1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>원전 관련 모멘텀에 대한 기대감과 함께 단기적인 조정 후 상승 가능성 언급. 일부 부정적 전망도 혼재.</t>
+          <t>외국인 매수세 유입 및 5일선, 20일선 지지 기반 상승 가능성 언급. 금리 인상 확정 및 CPI 발표 변수 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '120일선', '단기과열']</t>
+          <t>['외국인 매수', '5일선', 'CPI 발표']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7430</v>
+        <v>89900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.26%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="G15" t="n">
-        <v>206</v>
+        <v>674</v>
       </c>
       <c r="H15" t="n">
-        <v>11.72</v>
+        <v>23.59</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7680</v>
+        <v>91700</v>
       </c>
       <c r="K15" t="n">
-        <v>7540</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>7660</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7400</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>11.62</v>
+        <v>23.65</v>
       </c>
       <c r="O15" t="n">
-        <v>5932820035</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>8850</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4220</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-245000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>기관 및 외국인 매매 단가 분석과 저점 매수 기회 언급.</t>
+          <t>에너지 대미 투자 협상 마무리 및 29.7조 수주잔고 기반의 강력한 상승 기대감. 중동 에너지 공급망 불안 요인과 1호 투자 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['기관 매매', '저점 매수']</t>
+          <t>['에너지 대미 투자', '수주 잔고', '원전 사업']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15120</v>
+        <v>28750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.32%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G16" t="n">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>51.25</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>15640</v>
+        <v>29550</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>28650</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>28900</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>28500</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>24.99</v>
       </c>
       <c r="O16" t="n">
-        <v>12418000000</v>
+        <v>27716845475</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>31200</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="R16" t="n">
-        <v>23000</v>
+        <v>207000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-42000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>호남 반도체 부지 확보 및 메가 건설 관련 긍정적 전망. 친환경 특화 기업 투자 및 상승 추세 기대.</t>
+          <t>환율 하락 및 유가 상승 가능성 속 유럽 자금의 매수세 유입 기대. 단기 조정 불가피.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['금호건설', '반도체', '메가 건설']</t>
+          <t>['환율', '유가', '유럽 자금']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>259500</v>
+        <v>15040</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.71%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>45</v>
       </c>
       <c r="F17" t="n">
-        <v>501</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>2214</v>
+        <v>158</v>
       </c>
       <c r="H17" t="n">
-        <v>46.71</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>269500</v>
+        <v>15640</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>46.81</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>892163000000</v>
+        <v>13012000000</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1999,27 +1999,27 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-615000</v>
+        <v>23000</v>
       </c>
       <c r="S17" t="n">
-        <v>-530000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>매크로 및 FOMC 영향으로 인한 하락 전망과 JP모건의 저평가 분석 및 투자 의견 상향 언급. 게시판 분위기 혼조.</t>
+          <t>호남 반도체 클러스터 조성 사업 및 메가 건설 관련 호재. 친환경 특화 기업 투자.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['삼성전자', '매크로', 'JP모건']</t>
+          <t>['호남 반도체', '메가 건설', '친환경']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1783000</v>
+        <v>258500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.93%</t>
+          <t>-4.08%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="E18" t="n">
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>462</v>
+        <v>493</v>
       </c>
       <c r="G18" t="n">
-        <v>1339</v>
+        <v>2002</v>
       </c>
       <c r="H18" t="n">
-        <v>50.55</v>
+        <v>46.71</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1856000</v>
+        <v>269500</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2079,10 +2079,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>50.67</v>
+        <v>46.81</v>
       </c>
       <c r="O18" t="n">
-        <v>1506224000000</v>
+        <v>1013242000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2091,27 +2091,27 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-166000</v>
+        <v>-615000</v>
       </c>
       <c r="S18" t="n">
-        <v>-111000</v>
+        <v>-530000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>AI 클라우드 수요 폭발 관련 오라클 실적 발표에도 불구하고 하락세 지속. 저점 매수 및 분할 매수 전략 고려.</t>
+          <t>JP모건의 삼성전자 목표가 상향 조정 및 저평가 분석. 수출 호조에도 주가 하락.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['SK하이닉스', 'AI', '오라클']</t>
+          <t>['JP모건', '저평가', '수출']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,46 +2120,46 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28750</v>
+        <v>1779000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.12%</t>
+          <t>-4.15%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="E19" t="n">
-        <v>144</v>
+        <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>70</v>
+        <v>470</v>
       </c>
       <c r="G19" t="n">
-        <v>229</v>
+        <v>1319</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32</v>
+        <v>50.55</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>30300</v>
+        <v>1856000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2171,10 +2171,10 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.33</v>
+        <v>50.67</v>
       </c>
       <c r="O19" t="n">
-        <v>223240000000</v>
+        <v>1624411000000</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2183,27 +2183,27 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2000</v>
+        <v>-166000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-111000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>개인 투자자들의 긍정적 기대감이 높은 가운데, 단기적인 수급 개선 및 신규주로서의 잠재력에 대한 언급. 그러나 구체적인 근거 제시 미흡.</t>
+          <t>AI 클라우드 수요 폭발 뉴스에도 주가 하락. ADR 상승 및 반도체 수출 호조.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['수급', '신규주']</t>
+          <t>['AI 클라우드', 'ADR', '반도체 수출']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9280</v>
+        <v>3670</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-5.05%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="H20" t="n">
-        <v>4.49</v>
+        <v>0.73</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>9800</v>
+        <v>3865</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2263,10 +2263,10 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.42</v>
+        <v>1.54</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>33265000000</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2275,14 +2275,14 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-41000</v>
+        <v>214000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>수상 소식 언급에도 불구하고 주가 하락 및 거래량 증가에 대한 의구심 표출. 실질적인 호재나 뉴스 부재 속 관망세.</t>
+          <t>미국 증시 폭락 및 개인 투자자들의 탈출 시도. 일부 긍정적 기대감은 있으나, 거래량 감소 및 5일선 붕괴로 하락 추세.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['수상', '거래량', '호재']</t>
+          <t>['미국 증시', '거래량 감소', '하락 추세']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12080</v>
+        <v>28700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-7.29%</t>
+          <t>-5.28%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="G21" t="n">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13030</v>
+        <v>30300</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2355,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="O21" t="n">
-        <v>30853000000</v>
+        <v>235343000000</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2367,27 +2367,27 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-94000</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 테마 내 다른 종목(한전기술, TCC스틸)의 강세 속에서 삼미금속의 상대적 부진 및 거래량 부족에 대한 언급. 일부 매수 기회 언급.</t>
+          <t>타 급등주 대비 상대적 강세 및 저점 매수세 유입. 신규주로서의 기대감과 3일간의 조정 후 수급 개선 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '테마', '거래량']</t>
+          <t>['신규주', '수급 개선', '저점 매수']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>233500</v>
+        <v>191800</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-7.71%</t>
+          <t>-5.52%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="F22" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>484</v>
+        <v>61</v>
       </c>
       <c r="H22" t="n">
-        <v>7.58</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>253000</v>
+        <v>203000</v>
       </c>
       <c r="K22" t="n">
-        <v>241000</v>
+        <v>195000</v>
       </c>
       <c r="L22" t="n">
-        <v>241000</v>
+        <v>195600</v>
       </c>
       <c r="M22" t="n">
-        <v>231000</v>
+        <v>191700</v>
       </c>
       <c r="N22" t="n">
-        <v>8.539999999999999</v>
+        <v>75.92</v>
       </c>
       <c r="O22" t="n">
-        <v>115476938000</v>
+        <v>270018290750</v>
       </c>
       <c r="P22" t="n">
-        <v>426000</v>
+        <v>243500</v>
       </c>
       <c r="Q22" t="n">
-        <v>86100</v>
+        <v>58600</v>
       </c>
       <c r="R22" t="n">
-        <v>-224000</v>
+        <v>-405000</v>
       </c>
       <c r="S22" t="n">
-        <v>-14000</v>
+        <v>-52000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 하락 및 공매도에 대한 불만 표출. 회사 차원의 자사주 매입 소각, 무증 발표 요구. 긍정적인 뉴스나 근거는 부족.</t>
+          <t>미국 증시 하락 및 기관/외국인 매도세 속 주가 하락 우려. 우선주의 피난처 역할 기대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['공매도', '자사주', '매수']</t>
+          <t>['미국 증시', '기관 매도', '우선주']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2487,6 +2487,190 @@
         </is>
       </c>
       <c r="Z22" t="inlineStr">
+        <is>
+          <t>005935</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>12150</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-6.75%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>51</v>
+      </c>
+      <c r="F23" t="n">
+        <v>35</v>
+      </c>
+      <c r="G23" t="n">
+        <v>55</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>13030</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="O23" t="n">
+        <v>31446000000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-94000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>원전 테마 수급 쏠림 현상 속에서 타 종목 대비 부진. 석유 테마 대비 상대적 열세이며, 공매도 물량과 주포의 움직임에 대한 언급.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['원전 테마', '공매도', '주포']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>012210</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>232750</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-8.00%</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="E24" t="n">
+        <v>148</v>
+      </c>
+      <c r="F24" t="n">
+        <v>79</v>
+      </c>
+      <c r="G24" t="n">
+        <v>496</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>253000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>241000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>241000</v>
+      </c>
+      <c r="M24" t="n">
+        <v>231000</v>
+      </c>
+      <c r="N24" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="O24" t="n">
+        <v>119537097500</v>
+      </c>
+      <c r="P24" t="n">
+        <v>426000</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>86100</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-224000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-14000</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>CPI 발표 후 조정 예상 속 공매도 세력의 공격 및 개미 털기 의혹. 반도체 반등 흐름은 유지될 것이라는 전망과 함께 기관 매수세 관찰.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>['공매도', 'CPI 발표', '기관 매수']</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>042700</t>
         </is>

--- a/data/trending_integrated_20260911_10.xlsx
+++ b/data/trending_integrated_20260911_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>15620</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>+26.38%</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="E2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G2" t="n">
+        <v>72</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>12360</v>
+      </c>
+      <c r="K2" t="n">
+        <v>12800</v>
+      </c>
+      <c r="L2" t="n">
         <v>15650</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>+29.45%</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="E2" t="n">
-        <v>262</v>
-      </c>
-      <c r="F2" t="n">
-        <v>159</v>
-      </c>
-      <c r="G2" t="n">
-        <v>668</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>12090</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>12690</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03</v>
+        <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>147556000000</v>
+        <v>170571219815</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="R2" t="n">
-        <v>-347000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 국제 유가 폭등으로 인한 3연상 기대감. WTI 100달러 돌파 및 추가 상승 가능성 언급.</t>
+          <t>젠슨 황의 사이버 보안 시장 지목에 따른 기대감, 양자 보안 테마 부각 및 급등 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['흥구석유', '국제 유가', '중동 전쟁']</t>
+          <t>['사이버 보안', '젠슨 황', '양자 보안']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,86 +648,86 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15150</v>
+        <v>135800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+22.57%</t>
+          <t>+16.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.22</v>
+        <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H3" t="n">
-        <v>2.39</v>
+        <v>4.32</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12360</v>
+        <v>116300</v>
       </c>
       <c r="K3" t="n">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>15380</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>12690</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>4.58</v>
       </c>
       <c r="O3" t="n">
-        <v>152905425730</v>
+        <v>366301000000</v>
       </c>
       <c r="P3" t="n">
-        <v>30550</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-139000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>PQC 암호모듈 KCMVP 인증 획득 및 미국 양자보안 시장 진출. 젠슨황 발언 관련 기대감.</t>
+          <t>애플 관련 호재로 인한 주가 상승, 단기 급등에 대한 기대와 경계 혼재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['PQC', '양자보안', '젠슨황']</t>
+          <t>['애플', '단기 급등', '손바뀜']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,46 +740,46 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>138400</v>
+        <v>8300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+19.00%</t>
+          <t>+11.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.26</v>
+        <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>135</v>
+        <v>560</v>
       </c>
       <c r="H4" t="n">
-        <v>4.32</v>
+        <v>1.29</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>116300</v>
+        <v>7420</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.58</v>
+        <v>1.17</v>
       </c>
       <c r="O4" t="n">
-        <v>353434000000</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -803,27 +803,27 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>75000</v>
+        <v>20000</v>
       </c>
       <c r="S4" t="n">
-        <v>87000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>애플 및 무라타 관련 기대감으로 인한 급등. 손바뀜 및 차트 분석.</t>
+          <t>WCLC 학회 미친 데이터 발표 기대감. 기술 수출 가능성 및 14일 일정 관련 주목.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['애플', '무라타', '손바뀜']</t>
+          <t>['임상', '기술 수출', '발표']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,46 +832,46 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8300</v>
+        <v>1950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+10.80%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="E5" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>549</v>
+        <v>113</v>
       </c>
       <c r="H5" t="n">
-        <v>1.29</v>
+        <v>2.44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7420</v>
+        <v>1760</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.17</v>
+        <v>2.12</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>33233000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -895,27 +895,27 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>20000</v>
+        <v>-1017000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>중요 임상 데이터 발표(9월 14일) 및 기술 수출 가능성에 대한 기대감. 제약·바이오 섹터 전반의 강세 속에서 주목.</t>
+          <t>국제유가 상승 및 전쟁 테마 관련 기대감. 장금상선 보유 수량 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['임상', '데이터', '기술수출']</t>
+          <t>['전쟁 테마', '국제유가', '장금상선']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7680</v>
+        <v>15720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+8.34%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>3.11</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="G6" t="n">
-        <v>231</v>
+        <v>679</v>
       </c>
       <c r="H6" t="n">
-        <v>11.72</v>
+        <v>3.14</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7100</v>
+        <v>14510</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>17010</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>17310</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>15600</v>
       </c>
       <c r="N6" t="n">
-        <v>11.62</v>
+        <v>0.03</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>150250079130</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>36200</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>8920</v>
       </c>
       <c r="R6" t="n">
-        <v>100000</v>
+        <v>-347000</v>
       </c>
       <c r="S6" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외국인/기관 평균 매매단가 분석 결과 제시. 신영증권 출몰에 따른 개미들의 혼비백산 및 주가 조작 의혹 제기.</t>
+          <t>중동 전쟁 및 국제 유가 폭등으로 인한 3연상 기대감. WTI 100달러 돌파 및 추가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인/기관', '매매단가', '주가 조작']</t>
+          <t>['흥구석유', '국제 유가', '중동 전쟁']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10000</v>
+        <v>53400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+7.76%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.44</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>208</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>4.49</v>
+        <v>2.92</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9280</v>
+        <v>53200</v>
       </c>
       <c r="K7" t="n">
-        <v>10030</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10880</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.42</v>
+        <v>3.36</v>
       </c>
       <c r="O7" t="n">
-        <v>18459975900</v>
+        <v>57512000000</v>
       </c>
       <c r="P7" t="n">
-        <v>15640</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5470</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-41000</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>프리갈리앙 베스트 의료기술상 수상이라는 호재에도 불구하고 주가 하락. 공매도 세력과의 승부 및 역대급 거래량 기대감 언급.</t>
+          <t>미국 태양광 흐름에 따른 등락, 54 돌파 시 상방 추세 전환 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['프리갈리앙 수상', '의료 기술', '공매도']</t>
+          <t>['태양광', '상방 추세', '돌파']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1938</v>
+        <v>19490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.32</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G8" t="n">
-        <v>112</v>
+        <v>313</v>
       </c>
       <c r="H8" t="n">
-        <v>2.44</v>
+        <v>10.65</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1901</v>
+        <v>19450</v>
       </c>
       <c r="K8" t="n">
-        <v>2050</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2080</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1933</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>10.64</v>
       </c>
       <c r="O8" t="n">
-        <v>32314373114</v>
+        <v>58636000000</v>
       </c>
       <c r="P8" t="n">
-        <v>4795</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1524</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-1017000</v>
+        <v>-249000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>국제유가 상승 및 전쟁 테마 관련 기대감. 장금상선 보유 수량 언급.</t>
+          <t>NH투자증권의 목표주가 상향 조정. 대차해지 운동 동참 촉구.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['전쟁 테마', '국제유가', '장금상선']</t>
+          <t>['NH투자증권', '목표주가', '대차해지']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53400</v>
+        <v>14990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="H9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>53200</v>
+        <v>15040</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>14550</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>15260</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>14350</v>
       </c>
       <c r="N9" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>50042000000</v>
+        <v>13589247275</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>19380</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="R9" t="n">
-        <v>-14000</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 태양광 섹터 흐름 양호 및 양자보안 테마 기대감. SK와 자본력 콜라보.</t>
+          <t>호남 메가 건설 및 반도체 클러스터 조성 관련 기대감, 폐기물 처리 및 수소 생산 사업 부각.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['태양광', '양자보안', 'SK']</t>
+          <t>['메가 건설', '반도체 클러스터', '폐기물 처리']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19470</v>
+        <v>415500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="E10" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="F10" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="H10" t="n">
-        <v>10.65</v>
+        <v>38.02</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19450</v>
+        <v>417500</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>10.64</v>
+        <v>37.82</v>
       </c>
       <c r="O10" t="n">
-        <v>56975000000</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1355,27 +1355,27 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-249000</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NH투자증권의 목표주가 상향 조정. 대차해지 운동 동참 촉구.</t>
+          <t>아틀라스 관절부품 전량 수주 및 로봇 사업 확장. 유럽 중국차 관세 반사이익 및 미래차 신기술 공개.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['NH투자증권', '목표주가', '대차해지']</t>
+          <t>['로봇', '수주', '미래차']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>415500</v>
+        <v>50100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>185</v>
+        <v>414</v>
       </c>
       <c r="H11" t="n">
-        <v>38.02</v>
+        <v>38.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>417500</v>
+        <v>50400</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>50500</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>50600</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>49650</v>
       </c>
       <c r="N11" t="n">
-        <v>37.82</v>
+        <v>38.69</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>34096828875</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>67300</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>23150</v>
       </c>
       <c r="R11" t="n">
-        <v>5000</v>
+        <v>-110000</v>
       </c>
       <c r="S11" t="n">
-        <v>1000</v>
+        <v>-4000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>로봇 관절 부품 수주 및 미래차·로봇 신기술 공개 등 구체적인 호재 언급. 저평가 및 유럽 중국차 관세 관련 반사이익 기대.</t>
+          <t>약 4.7조 원 규모의 대규모 수주 공시 확인. 사우디, 베트남 등 겹호재와 외국인 매수세 언급. 긍정적 추세 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['로봇', '수주', '미래차']</t>
+          <t>['수주', '공시', '외국인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49950</v>
+        <v>14170</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="H12" t="n">
-        <v>38.78</v>
+        <v>5.98</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>50400</v>
+        <v>14320</v>
       </c>
       <c r="K12" t="n">
-        <v>50500</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>50600</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>49650</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>38.69</v>
+        <v>6.09</v>
       </c>
       <c r="O12" t="n">
-        <v>33201786050</v>
+        <v>64016000000</v>
       </c>
       <c r="P12" t="n">
-        <v>67300</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>23150</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-110000</v>
+        <v>-297000</v>
       </c>
       <c r="S12" t="n">
-        <v>-4000</v>
+        <v>-61000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>약 4.7조 원 규모의 대규모 수주 공시 확인. 사우디, 베트남 등 겹호재와 외국인 매수세 언급. 긍정적 추세 전망.</t>
+          <t>원전 관련 테마 기대감 속에서 모건 스탠리의 대량 매수 관측. 단기 과열 우려도 있으나, 원전주의 강력한 재료 기반 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '공시', '외국인']</t>
+          <t>['원전 테마', '모건 스탠리', '수주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,46 +1568,46 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14120</v>
+        <v>8810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-1.56%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.11</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>374</v>
+        <v>151</v>
       </c>
       <c r="H13" t="n">
-        <v>5.98</v>
+        <v>27.19</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14320</v>
+        <v>8950</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6.09</v>
+        <v>27.16</v>
       </c>
       <c r="O13" t="n">
-        <v>62497000000</v>
+        <v>7899000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1631,27 +1631,27 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-297000</v>
+        <v>-28000</v>
       </c>
       <c r="S13" t="n">
-        <v>-61000</v>
+        <v>-33000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>원전 관련 테마 기대감 속에서 모건 스탠리의 대량 매수 관측. 단기 과열 우려도 있으나, 원전주의 강력한 재료 기반 상승 가능성 언급.</t>
+          <t>지속적인 주가 하락 및 부진, 금리 인상 가능성에 대한 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전 테마', '모건 스탠리', '수주']</t>
+          <t>['주가 부진', '금리 인상', '저평가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,46 +1660,46 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14740</v>
+        <v>89900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.39</v>
+        <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="G14" t="n">
-        <v>141</v>
+        <v>694</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>23.59</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14960</v>
+        <v>91700</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.89</v>
+        <v>23.65</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1723,23 +1723,23 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-34000</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 및 5일선, 20일선 지지 기반 상승 가능성 언급. 금리 인상 확정 및 CPI 발표 변수 존재.</t>
+          <t>에너지 대미 투자 협상 마무리 및 원전 수주 기대감. 수주잔고 규모 증가 및 중동 에너지 공급망 이슈.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외국인 매수', '5일선', 'CPI 발표']</t>
+          <t>['원전', '수주', '대미 투자']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,86 +1752,86 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>89900</v>
+        <v>14230</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.06</v>
+        <v>-0.39</v>
       </c>
       <c r="E15" t="n">
-        <v>152</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>674</v>
+        <v>143</v>
       </c>
       <c r="H15" t="n">
-        <v>23.59</v>
+        <v>2.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>91700</v>
+        <v>14740</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>14050</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>14450</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>14030</v>
       </c>
       <c r="N15" t="n">
-        <v>23.65</v>
+        <v>2.89</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>27804658280</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>-245000</v>
+        <v>-34000</v>
       </c>
       <c r="S15" t="n">
-        <v>10000</v>
+        <v>-1000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>에너지 대미 투자 협상 마무리 및 29.7조 수주잔고 기반의 강력한 상승 기대감. 중동 에너지 공급망 불안 요인과 1호 투자 가능성 언급.</t>
+          <t>외국인 매수세 유입 및 5일선, 20일선 지지 기반 확인. 단기 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['에너지 대미 투자', '수주 잔고', '원전 사업']</t>
+          <t>['외국인', '지지선', '단기 상승']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1859,23 +1859,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G16" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H16" t="n">
-        <v>51.25</v>
+        <v>25.55</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,28 +1883,28 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>29550</v>
+        <v>29800</v>
       </c>
       <c r="K16" t="n">
-        <v>28650</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>28900</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>28500</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>24.99</v>
       </c>
       <c r="O16" t="n">
-        <v>27716845475</v>
+        <v>28527000000</v>
       </c>
       <c r="P16" t="n">
-        <v>31200</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>207000</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>환율 하락 및 유가 상승 가능성 속 유럽 자금의 매수세 유입 기대. 단기 조정 불가피.</t>
+          <t>환율 하락 및 유가 상승 예상, 외인 매수세 유입에 따른 단기 조정 후 반등 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['환율', '유가', '유럽 자금']</t>
+          <t>['환율', '유가', '외인 매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15040</v>
+        <v>7400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-3.65%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>158</v>
+        <v>247</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>11.72</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>15640</v>
+        <v>7680</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>7540</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>7660</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>7390</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>11.62</v>
       </c>
       <c r="O17" t="n">
-        <v>13012000000</v>
+        <v>6615392210</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>8850</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4220</v>
       </c>
       <c r="R17" t="n">
-        <v>23000</v>
+        <v>100000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 조성 사업 및 메가 건설 관련 호재. 친환경 특화 기업 투자.</t>
+          <t>기관 및 외국인 평균 매매 단가 분석. 금호주포 존재 가능성 언급 및 주가 조작 의혹.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['호남 반도체', '메가 건설', '친환경']</t>
+          <t>['기관', '외국인', '주가 조작']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>258500</v>
+        <v>1780000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.08%</t>
+          <t>-3.94%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="E18" t="n">
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="G18" t="n">
-        <v>2002</v>
+        <v>1188</v>
       </c>
       <c r="H18" t="n">
-        <v>46.71</v>
+        <v>50.55</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>269500</v>
+        <v>1853000</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1773000</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1795000</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1768000</v>
       </c>
       <c r="N18" t="n">
-        <v>46.81</v>
+        <v>50.67</v>
       </c>
       <c r="O18" t="n">
-        <v>1013242000000</v>
+        <v>1758972399000</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>305500</v>
       </c>
       <c r="R18" t="n">
-        <v>-615000</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-530000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>JP모건의 삼성전자 목표가 상향 조정 및 저평가 분석. 수출 호조에도 주가 하락.</t>
+          <t>AI 클라우드 수요 증가 뉴스에도 불구하고 주가 하락, 네이버 증권 UI 변경에 대한 불만.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['JP모건', '저평가', '수출']</t>
+          <t>['AI 클라우드', '주가 하락', '네이버 증권']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779000</v>
+        <v>12120</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.15%</t>
+          <t>-4.04%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.12</v>
+        <v>0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="F19" t="n">
-        <v>470</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>1319</v>
+        <v>55</v>
       </c>
       <c r="H19" t="n">
-        <v>50.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1856000</v>
+        <v>12630</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>12520</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>12930</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>12070</v>
       </c>
       <c r="N19" t="n">
-        <v>50.67</v>
+        <v>0.14</v>
       </c>
       <c r="O19" t="n">
-        <v>1624411000000</v>
+        <v>31788640945</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>20850</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4020</v>
       </c>
       <c r="R19" t="n">
-        <v>-166000</v>
+        <v>-94000</v>
       </c>
       <c r="S19" t="n">
-        <v>-111000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>AI 클라우드 수요 폭발 뉴스에도 주가 하락. ADR 상승 및 반도체 수출 호조.</t>
+          <t>원전 테마 내에서 한전기술 대비 상대적 약세. 공매도 수량 증가 및 시간 끌기 예상.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['AI 클라우드', 'ADR', '반도체 수출']</t>
+          <t>['원전', '공매도', '테마']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,46 +2212,46 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3670</v>
+        <v>257750</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.05%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>493</v>
       </c>
       <c r="G20" t="n">
-        <v>85</v>
+        <v>1877</v>
       </c>
       <c r="H20" t="n">
-        <v>0.73</v>
+        <v>46.71</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3865</v>
+        <v>269500</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2263,10 +2263,10 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.54</v>
+        <v>46.81</v>
       </c>
       <c r="O20" t="n">
-        <v>33265000000</v>
+        <v>1160235000000</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2275,14 +2275,14 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>214000</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 개인 투자자들의 탈출 시도. 일부 긍정적 기대감은 있으나, 거래량 감소 및 5일선 붕괴로 하락 추세.</t>
+          <t>반도체 수출 역대 최대에도 불구하고 주가 하락, 네이버 증권 UI 변경에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['미국 증시', '거래량 감소', '하락 추세']</t>
+          <t>['반도체 수출', '주가 하락', '네이버 증권']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2326,13 +2326,13 @@
         <v>-0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F21" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G21" t="n">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="H21" t="n">
         <v>0.32</v>
@@ -2358,7 +2358,7 @@
         <v>0.33</v>
       </c>
       <c r="O21" t="n">
-        <v>235343000000</v>
+        <v>239659000000</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2367,23 +2367,23 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>타 급등주 대비 상대적 강세 및 저점 매수세 유입. 신규주로서의 기대감과 3일간의 조정 후 수급 개선 전망.</t>
+          <t>거래량 돌파 및 3일간 조정 후 수급 개선 전망. 신규주로서의 기대감 형성.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['신규주', '수급 개선', '저점 매수']</t>
+          <t>['거래량', '수급', '신규주']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2403,83 +2403,83 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>191800</v>
+        <v>9280</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.52%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G22" t="n">
-        <v>61</v>
+        <v>211</v>
       </c>
       <c r="H22" t="n">
-        <v>75.98999999999999</v>
+        <v>4.49</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>203000</v>
+        <v>9800</v>
       </c>
       <c r="K22" t="n">
-        <v>195000</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>195600</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>191700</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>75.92</v>
+        <v>4.42</v>
       </c>
       <c r="O22" t="n">
-        <v>270018290750</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>243500</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-405000</v>
+        <v>-41000</v>
       </c>
       <c r="S22" t="n">
-        <v>-52000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 증시 하락 및 기관/외국인 매도세 속 주가 하락 우려. 우선주의 피난처 역할 기대.</t>
+          <t>프리갈리앙 베스트 의료기술상 수상이라는 호재에도 불구하고 주가 하락. 공매도 세력과의 승부 및 역대급 거래량 기대감 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['미국 증시', '기관 매도', '우선주']</t>
+          <t>['프리갈리앙 수상', '의료 기술', '공매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12150</v>
+        <v>3647</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-6.75%</t>
+          <t>-5.64%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>13030</v>
+        <v>3865</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.14</v>
+        <v>1.54</v>
       </c>
       <c r="O23" t="n">
-        <v>31446000000</v>
+        <v>33734000000</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2551,14 +2551,14 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-94000</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>원전 테마 수급 쏠림 현상 속에서 타 종목 대비 부진. 석유 테마 대비 상대적 열세이며, 공매도 물량과 주포의 움직임에 대한 언급.</t>
+          <t>미국 증시 폭락 및 바이오 섹터 전반의 하락세, 희망적인 전망과 경계 의견 혼재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['원전 테마', '공매도', '주포']</t>
+          <t>['미국 증시', '바이오 섹터', '하락세']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>232750</v>
+        <v>191500</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-8.00%</t>
+          <t>-5.67%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>148</v>
+        <v>61</v>
       </c>
       <c r="F24" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="G24" t="n">
-        <v>496</v>
+        <v>74</v>
       </c>
       <c r="H24" t="n">
-        <v>7.58</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,47 +2619,47 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>253000</v>
+        <v>203000</v>
       </c>
       <c r="K24" t="n">
-        <v>241000</v>
+        <v>195000</v>
       </c>
       <c r="L24" t="n">
-        <v>241000</v>
+        <v>195600</v>
       </c>
       <c r="M24" t="n">
-        <v>231000</v>
+        <v>191000</v>
       </c>
       <c r="N24" t="n">
-        <v>8.539999999999999</v>
+        <v>75.92</v>
       </c>
       <c r="O24" t="n">
-        <v>119537097500</v>
+        <v>293655494950</v>
       </c>
       <c r="P24" t="n">
-        <v>426000</v>
+        <v>243500</v>
       </c>
       <c r="Q24" t="n">
-        <v>86100</v>
+        <v>58600</v>
       </c>
       <c r="R24" t="n">
-        <v>-224000</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-14000</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>CPI 발표 후 조정 예상 속 공매도 세력의 공격 및 개미 털기 의혹. 반도체 반등 흐름은 유지될 것이라는 전망과 함께 기관 매수세 관찰.</t>
+          <t>기관/외인 매도세 속 주가 하락, 미국 증시 영향 및 네이버 증권 UI 변경 불만.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['공매도', 'CPI 발표', '기관 매수']</t>
+          <t>['기관 매도', '외인 매도', '주가 하락']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2671,6 +2671,98 @@
         </is>
       </c>
       <c r="Z24" t="inlineStr">
+        <is>
+          <t>005935</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>232500</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-8.10%</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="E25" t="n">
+        <v>154</v>
+      </c>
+      <c r="F25" t="n">
+        <v>84</v>
+      </c>
+      <c r="G25" t="n">
+        <v>511</v>
+      </c>
+      <c r="H25" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>253000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>241000</v>
+      </c>
+      <c r="L25" t="n">
+        <v>241000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>231000</v>
+      </c>
+      <c r="N25" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="O25" t="n">
+        <v>124311998750</v>
+      </c>
+      <c r="P25" t="n">
+        <v>426000</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>86100</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-224000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-14000</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>CPI 발표 후 조정 예상 속 공매도 세력의 공격 및 개미 털기 의혹. 반도체 반등 흐름은 유지될 것이라는 전망과 함께 기관 매수세 관찰.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>['공매도', 'CPI 발표', '기관 매수']</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>042700</t>
         </is>

--- a/data/trending_integrated_20260911_10.xlsx
+++ b/data/trending_integrated_20260911_10.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15620</v>
+        <v>15440</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+26.38%</t>
+          <t>+27.71%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.22</v>
+        <v>3.11</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>291</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="G2" t="n">
-        <v>72</v>
+        <v>688</v>
       </c>
       <c r="H2" t="n">
-        <v>2.39</v>
+        <v>3.14</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12360</v>
+        <v>12090</v>
       </c>
       <c r="K2" t="n">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>15650</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>12690</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.61</v>
+        <v>0.03</v>
       </c>
       <c r="O2" t="n">
-        <v>170571219815</v>
+        <v>155533000000</v>
       </c>
       <c r="P2" t="n">
-        <v>30550</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-347000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>젠슨 황의 사이버 보안 시장 지목에 따른 기대감, 양자 보안 테마 부각 및 급등 전망.</t>
+          <t>중동 전쟁 및 국제 유가 폭등으로 인한 3연상 기대감. WTI 100달러 돌파 및 추가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['사이버 보안', '젠슨 황', '양자 보안']</t>
+          <t>['흥구석유', '국제 유가', '중동 전쟁']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,46 +648,46 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135800</v>
+        <v>16060</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+16.77%</t>
+          <t>+27.36%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.26</v>
+        <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="H3" t="n">
-        <v>4.32</v>
+        <v>2.39</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>116300</v>
+        <v>12610</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.58</v>
+        <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>366301000000</v>
+        <v>198459000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -711,23 +711,23 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-139000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>애플 관련 호재로 인한 주가 상승, 단기 급등에 대한 기대와 경계 혼재.</t>
+          <t>Nvidia CEO의 사이버 보안 섹터 지목으로 양자 보안 관련주로 부각되며 급등, 향후 추가 상승 기대감이 높음.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['애플', '단기 급등', '손바뀜']</t>
+          <t>['사이버 보안', '양자 보안', '젠슨 황']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,46 +740,46 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8300</v>
+        <v>137700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+18.40%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="E4" t="n">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
-        <v>560</v>
+        <v>142</v>
       </c>
       <c r="H4" t="n">
-        <v>1.29</v>
+        <v>4.32</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7420</v>
+        <v>116300</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.17</v>
+        <v>4.58</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>373263000000</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -803,27 +803,27 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>20000</v>
+        <v>75000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>WCLC 학회 미친 데이터 발표 기대감. 기술 수출 가능성 및 14일 일정 관련 주목.</t>
+          <t>애플 관련주 또는 무라타 제작소와의 연관성으로 상승했으나, 단기 급등 후 차익 실현 매물이 출현함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['임상', '기술 수출', '발표']</t>
+          <t>['애플', '무라타 제작소', '손바뀜']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,46 +832,46 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1950</v>
+        <v>8300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+10.80%</t>
+          <t>+11.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>113</v>
+        <v>541</v>
       </c>
       <c r="H5" t="n">
-        <v>2.44</v>
+        <v>1.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1760</v>
+        <v>7420</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.12</v>
+        <v>1.17</v>
       </c>
       <c r="O5" t="n">
-        <v>33233000000</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -895,27 +895,27 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-1017000</v>
+        <v>20000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>국제유가 상승 및 전쟁 테마 관련 기대감. 장금상선 보유 수량 언급.</t>
+          <t>임상 시험 디자인 발표 및 기술 수출 가능성 언급. 9월 14일 예정된 데이터 발표에 대한 높은 기대감으로 상승 가능성 부각.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['전쟁 테마', '국제유가', '장금상선']</t>
+          <t>['임상', '기술 수출', '발표']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15720</v>
+        <v>1930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+8.34%</t>
+          <t>+9.66%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.11</v>
+        <v>0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>276</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
-        <v>166</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
-        <v>679</v>
+        <v>125</v>
       </c>
       <c r="H6" t="n">
-        <v>3.14</v>
+        <v>2.44</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14510</v>
+        <v>1760</v>
       </c>
       <c r="K6" t="n">
-        <v>17010</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>17310</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>150250079130</v>
+        <v>34096000000</v>
       </c>
       <c r="P6" t="n">
-        <v>36200</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8920</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-347000</v>
+        <v>-1017000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 국제 유가 폭등으로 인한 3연상 기대감. WTI 100달러 돌파 및 추가 상승 가능성 언급.</t>
+          <t>홍해 사태와 유가 상승 관련주로 부각되며 단기 급등 후 변동성을 보이는 상황.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['흥구석유', '국제 유가', '중동 전쟁']</t>
+          <t>['전쟁 테마주', '국제 유가', '홍해 사태']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53400</v>
+        <v>28400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+8.81%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.44</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>302</v>
       </c>
       <c r="H7" t="n">
-        <v>2.92</v>
+        <v>0.32</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>53200</v>
+        <v>26100</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>26350</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>30300</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>25400</v>
       </c>
       <c r="N7" t="n">
-        <v>3.36</v>
+        <v>0.33</v>
       </c>
       <c r="O7" t="n">
-        <v>57512000000</v>
+        <v>245462884725</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>39350</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 태양광 흐름에 따른 등락, 54 돌파 시 상방 추세 전환 기대.</t>
+          <t>신규 상장 종목으로, 기존 급등주 대비 양호한 흐름을 보이며 수급 개선에 대한 기대감 형성. 3일간 조정 후 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['태양광', '상방 추세', '돌파']</t>
+          <t>['급등주', '수급', '신규주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19490</v>
+        <v>9920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+6.90%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>313</v>
+        <v>212</v>
       </c>
       <c r="H8" t="n">
-        <v>10.65</v>
+        <v>4.49</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>19450</v>
+        <v>9280</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>10030</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>10880</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="N8" t="n">
-        <v>10.64</v>
+        <v>4.42</v>
       </c>
       <c r="O8" t="n">
-        <v>58636000000</v>
+        <v>19305264890</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>15640</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5470</v>
       </c>
       <c r="R8" t="n">
-        <v>-249000</v>
+        <v>-41000</v>
       </c>
       <c r="S8" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>NH투자증권의 목표주가 상향 조정. 대차해지 운동 동참 촉구.</t>
+          <t>프리갈리앙 베스트 의료기술상 수상이라는 호재에도 불구하고 주가 하락. 공매도 세력과의 승부 및 역대급 거래량 기대감 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['NH투자증권', '목표주가', '대차해지']</t>
+          <t>['프리갈리앙 수상', '의료 기술', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14990</v>
+        <v>53100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+2.51%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>180</v>
+        <v>86</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>15040</v>
+        <v>51800</v>
       </c>
       <c r="K9" t="n">
-        <v>14550</v>
+        <v>51300</v>
       </c>
       <c r="L9" t="n">
-        <v>15260</v>
+        <v>53900</v>
       </c>
       <c r="M9" t="n">
-        <v>14350</v>
+        <v>51300</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O9" t="n">
-        <v>13589247275</v>
+        <v>59744322500</v>
       </c>
       <c r="P9" t="n">
-        <v>19380</v>
+        <v>87700</v>
       </c>
       <c r="Q9" t="n">
-        <v>3200</v>
+        <v>17210</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-14000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>호남 메가 건설 및 반도체 클러스터 조성 관련 기대감, 폐기물 처리 및 수소 생산 사업 부각.</t>
+          <t>미국 태양광 섹터 흐름 속에서 주가 상승을 기대하나, 개인 매물 출회로 인한 변동성을 겪고 있음.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['메가 건설', '반도체 클러스터', '폐기물 처리']</t>
+          <t>['태양광', '개미 무덤', 'SK']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>415500</v>
+        <v>19640</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.98%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>190</v>
+        <v>331</v>
       </c>
       <c r="H10" t="n">
-        <v>38.02</v>
+        <v>10.65</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>417500</v>
+        <v>19450</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>37.82</v>
+        <v>10.64</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>60909000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1355,27 +1355,27 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-249000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>아틀라스 관절부품 전량 수주 및 로봇 사업 확장. 유럽 중국차 관세 반사이익 및 미래차 신기술 공개.</t>
+          <t>NH투자증권의 목표주가 상향 소식과 함께 '대차해지'를 통한 공매도 세력 대응 요구가 집중됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['로봇', '수주', '미래차']</t>
+          <t>['대차해지', '공매도', '목표주가 상향']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50100</v>
+        <v>416500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>414</v>
+        <v>192</v>
       </c>
       <c r="H11" t="n">
-        <v>38.78</v>
+        <v>38.02</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>50400</v>
+        <v>415500</v>
       </c>
       <c r="K11" t="n">
-        <v>50500</v>
+        <v>407000</v>
       </c>
       <c r="L11" t="n">
-        <v>50600</v>
+        <v>417500</v>
       </c>
       <c r="M11" t="n">
-        <v>49650</v>
+        <v>404000</v>
       </c>
       <c r="N11" t="n">
-        <v>38.69</v>
+        <v>37.82</v>
       </c>
       <c r="O11" t="n">
-        <v>34096828875</v>
+        <v>32736847750</v>
       </c>
       <c r="P11" t="n">
-        <v>67300</v>
+        <v>822000</v>
       </c>
       <c r="Q11" t="n">
-        <v>23150</v>
+        <v>283000</v>
       </c>
       <c r="R11" t="n">
-        <v>-110000</v>
+        <v>5000</v>
       </c>
       <c r="S11" t="n">
-        <v>-4000</v>
+        <v>1000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>약 4.7조 원 규모의 대규모 수주 공시 확인. 사우디, 베트남 등 겹호재와 외국인 매수세 언급. 긍정적 추세 전망.</t>
+          <t>아틀라스 관절부품 전량 수주 및 로봇 사업 확장. 유럽 중국차 관세 반사이익 및 미래차 신기술 공개.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주', '공시', '외국인']</t>
+          <t>['로봇', '수주', '미래차']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14170</v>
+        <v>90100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>159</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>381</v>
+        <v>680</v>
       </c>
       <c r="H12" t="n">
-        <v>5.98</v>
+        <v>23.59</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14320</v>
+        <v>89900</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>88700</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>90400</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="N12" t="n">
-        <v>6.09</v>
+        <v>23.65</v>
       </c>
       <c r="O12" t="n">
-        <v>64016000000</v>
+        <v>84062168800</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-297000</v>
+        <v>-245000</v>
       </c>
       <c r="S12" t="n">
-        <v>-61000</v>
+        <v>10000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>원전 관련 테마 기대감 속에서 모건 스탠리의 대량 매수 관측. 단기 과열 우려도 있으나, 원전주의 강력한 재료 기반 상승 가능성 언급.</t>
+          <t>미국 에너지 투자 협상 완료 및 수주 잔고 증가로 인한 기대감 부각. 원전 관련 긍정적 전망 및 목표가 상향 제시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전 테마', '모건 스탠리', '수주']</t>
+          <t>['에너지', '수주', '원전']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8810</v>
+        <v>3620</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="H13" t="n">
-        <v>27.19</v>
+        <v>0.73</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8950</v>
+        <v>3620</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3725</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3915</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3550</v>
       </c>
       <c r="N13" t="n">
-        <v>27.16</v>
+        <v>1.54</v>
       </c>
       <c r="O13" t="n">
-        <v>7899000000</v>
+        <v>34467093988</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4335</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="R13" t="n">
-        <v>-28000</v>
+        <v>214000</v>
       </c>
       <c r="S13" t="n">
-        <v>-33000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>지속적인 주가 하락 및 부진, 금리 인상 가능성에 대한 우려.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 부진', '금리 인상', '저평가']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>89900</v>
+        <v>50300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E14" t="n">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="F14" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="G14" t="n">
-        <v>694</v>
+        <v>417</v>
       </c>
       <c r="H14" t="n">
-        <v>23.59</v>
+        <v>38.78</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>91700</v>
+        <v>50400</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>50500</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>50600</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>49650</v>
       </c>
       <c r="N14" t="n">
-        <v>23.65</v>
+        <v>38.69</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>37145675825</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-110000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>에너지 대미 투자 협상 마무리 및 원전 수주 기대감. 수주잔고 규모 증가 및 중동 에너지 공급망 이슈.</t>
+          <t>약 4.7조 원 규모의 대규모 수주 공시 확인. 사우디, 베트남 등 겹호재와 외국인 매수세 언급. 긍정적 추세 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '수주', '대미 투자']</t>
+          <t>['수주', '공시', '외국인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14230</v>
+        <v>14930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
         <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>143</v>
+        <v>189</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14740</v>
+        <v>15040</v>
       </c>
       <c r="K15" t="n">
-        <v>14050</v>
+        <v>14550</v>
       </c>
       <c r="L15" t="n">
-        <v>14450</v>
+        <v>15260</v>
       </c>
       <c r="M15" t="n">
-        <v>14030</v>
+        <v>14350</v>
       </c>
       <c r="N15" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>27804658280</v>
+        <v>14291853775</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>-34000</v>
+        <v>23000</v>
       </c>
       <c r="S15" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 및 5일선, 20일선 지지 기반 확인. 단기 상승 가능성 언급.</t>
+          <t>호남 반도체 클러스터 부지 확보 및 메가 건설 관련 긍정적 뉴스 부각. 친환경 투자 및 건설 사업 확장으로 인한 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['외국인', '지지선', '단기 상승']</t>
+          <t>['반도체', '건설', '호남']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28750</v>
+        <v>8800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-1.90%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F16" t="n">
         <v>33</v>
       </c>
       <c r="G16" t="n">
-        <v>99</v>
+        <v>149</v>
       </c>
       <c r="H16" t="n">
-        <v>25.55</v>
+        <v>27.19</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>29800</v>
+        <v>8970</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>8780</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>8870</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>8680</v>
       </c>
       <c r="N16" t="n">
-        <v>24.99</v>
+        <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>28527000000</v>
+        <v>8982521055</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>207000</v>
+        <v>-28000</v>
       </c>
       <c r="S16" t="n">
-        <v>-42000</v>
+        <v>-33000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>환율 하락 및 유가 상승 예상, 외인 매수세 유입에 따른 단기 조정 후 반등 전망.</t>
+          <t>주가 상승에 대한 강한 불만과 함께 회사의 실적 부진 및 저평가에 대한 부정적인 인식이 지배적임.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['환율', '유가', '외인 매수']</t>
+          <t>['저평가', '실적 부진', '금리 인상']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7400</v>
+        <v>192400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-2.58%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>247</v>
+        <v>80</v>
       </c>
       <c r="H17" t="n">
-        <v>11.72</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>7680</v>
+        <v>197500</v>
       </c>
       <c r="K17" t="n">
-        <v>7540</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>7660</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>7390</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>11.62</v>
+        <v>75.92</v>
       </c>
       <c r="O17" t="n">
-        <v>6615392210</v>
+        <v>303479000000</v>
       </c>
       <c r="P17" t="n">
-        <v>8850</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4220</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>100000</v>
+        <v>-405000</v>
       </c>
       <c r="S17" t="n">
-        <v>-1000</v>
+        <v>-52000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>기관 및 외국인 평균 매매 단가 분석. 금호주포 존재 가능성 언급 및 주가 조작 의혹.</t>
+          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['기관', '외국인', '주가 조작']</t>
+          <t>['우선주', '기관 매도', '미국 증시']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1780000</v>
+        <v>14110</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.94%</t>
+          <t>-3.36%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>63</v>
       </c>
       <c r="F18" t="n">
-        <v>478</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>1188</v>
+        <v>385</v>
       </c>
       <c r="H18" t="n">
-        <v>50.55</v>
+        <v>5.98</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1853000</v>
+        <v>14600</v>
       </c>
       <c r="K18" t="n">
-        <v>1773000</v>
+        <v>14800</v>
       </c>
       <c r="L18" t="n">
-        <v>1795000</v>
+        <v>14950</v>
       </c>
       <c r="M18" t="n">
-        <v>1768000</v>
+        <v>14020</v>
       </c>
       <c r="N18" t="n">
-        <v>50.67</v>
+        <v>6.09</v>
       </c>
       <c r="O18" t="n">
-        <v>1758972399000</v>
+        <v>65394130630</v>
       </c>
       <c r="P18" t="n">
-        <v>2987000</v>
+        <v>30200</v>
       </c>
       <c r="Q18" t="n">
-        <v>305500</v>
+        <v>3540</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-297000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-61000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>AI 클라우드 수요 증가 뉴스에도 불구하고 주가 하락, 네이버 증권 UI 변경에 대한 불만.</t>
+          <t>원전 관련 테마 기대감 속에서 모건 스탠리의 대량 매수 관측. 단기 과열 우려도 있으나, 원전주의 강력한 재료 기반 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['AI 클라우드', '주가 하락', '네이버 증권']</t>
+          <t>['원전 테마', '모건 스탠리', '수주']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12120</v>
+        <v>14230</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.04%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.8</v>
+        <v>-0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>55</v>
+        <v>148</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>12630</v>
+        <v>14740</v>
       </c>
       <c r="K19" t="n">
-        <v>12520</v>
+        <v>14050</v>
       </c>
       <c r="L19" t="n">
-        <v>12930</v>
+        <v>14450</v>
       </c>
       <c r="M19" t="n">
-        <v>12070</v>
+        <v>14030</v>
       </c>
       <c r="N19" t="n">
-        <v>0.14</v>
+        <v>2.89</v>
       </c>
       <c r="O19" t="n">
-        <v>31788640945</v>
+        <v>28632174220</v>
       </c>
       <c r="P19" t="n">
-        <v>20850</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>4020</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-94000</v>
+        <v>-34000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>원전 테마 내에서 한전기술 대비 상대적 약세. 공매도 수량 증가 및 시간 끌기 예상.</t>
+          <t>외국인 매수세 및 프로그램 매수에 따른 상승 기대감 존재. 단기적인 상승 움직임 예측되나, 전반적인 증시 하락 분위기 속에 관망세 짙음.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '테마']</t>
+          <t>['외국인', '매수', '움직임']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>257750</v>
+        <v>7410</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>84</v>
       </c>
       <c r="F20" t="n">
-        <v>493</v>
+        <v>48</v>
       </c>
       <c r="G20" t="n">
-        <v>1877</v>
+        <v>261</v>
       </c>
       <c r="H20" t="n">
-        <v>46.71</v>
+        <v>11.72</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>269500</v>
+        <v>7680</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>7540</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>7660</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>7390</v>
       </c>
       <c r="N20" t="n">
-        <v>46.81</v>
+        <v>11.62</v>
       </c>
       <c r="O20" t="n">
-        <v>1160235000000</v>
+        <v>6952711385</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>8850</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4220</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>반도체 수출 역대 최대에도 불구하고 주가 하락, 네이버 증권 UI 변경에 대한 불만 제기.</t>
+          <t>기관의 매수 시그널 및 8000원 돌파 기대감 있으나, 전반적인 지수 하락 및 매도 물량 출회로 부정적 전망. 공매도 관련 언급 존재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['반도체 수출', '주가 하락', '네이버 증권']</t>
+          <t>['기관', '매수', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,14 +2304,14 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2319,31 +2319,31 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-5.28%</t>
+          <t>-3.69%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>158</v>
+        <v>42</v>
       </c>
       <c r="F21" t="n">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>281</v>
+        <v>103</v>
       </c>
       <c r="H21" t="n">
-        <v>0.32</v>
+        <v>25.55</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>30300</v>
+        <v>29800</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2355,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.33</v>
+        <v>24.99</v>
       </c>
       <c r="O21" t="n">
-        <v>239659000000</v>
+        <v>29471000000</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2367,27 +2367,27 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2000</v>
+        <v>207000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-42000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>거래량 돌파 및 3일간 조정 후 수급 개선 전망. 신규주로서의 기대감 형성.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['거래량', '수급', '신규주']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,46 +2396,46 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9280</v>
+        <v>1782000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-3.99%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>34</v>
+        <v>467</v>
       </c>
       <c r="G22" t="n">
-        <v>211</v>
+        <v>1141</v>
       </c>
       <c r="H22" t="n">
-        <v>4.49</v>
+        <v>50.55</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>9800</v>
+        <v>1856000</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.42</v>
+        <v>50.67</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1868848000000</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2459,27 +2459,27 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-41000</v>
+        <v>-166000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-111000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>프리갈리앙 베스트 의료기술상 수상이라는 호재에도 불구하고 주가 하락. 공매도 세력과의 승부 및 역대급 거래량 기대감 언급.</t>
+          <t>AI 클라우드 수요 증가 소식에도 불구하고 주가는 하락세를 보이며, 네이버 증권 인터페이스 변경에 대한 불만이 제기됨.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['프리갈리앙 수상', '의료 기술', '공매도']</t>
+          <t>['AI', '반도체 수출', '네이버 증권']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,77 +2488,77 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3647</v>
+        <v>258250</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.64%</t>
+          <t>-4.00%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>495</v>
       </c>
       <c r="G23" t="n">
-        <v>87</v>
+        <v>1841</v>
       </c>
       <c r="H23" t="n">
-        <v>0.73</v>
+        <v>46.71</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3865</v>
+        <v>269000</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>257500</v>
       </c>
       <c r="N23" t="n">
-        <v>1.54</v>
+        <v>46.81</v>
       </c>
       <c r="O23" t="n">
-        <v>33734000000</v>
+        <v>1252671497250</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>-615000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-530000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 바이오 섹터 전반의 하락세, 희망적인 전망과 경계 의견 혼재.</t>
+          <t>수출 호조에도 불구하고 주가는 부진하며, 네이버 증권 게시판 개편에 대한 불만이 제기됨.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['미국 증시', '바이오 섹터', '하락세']</t>
+          <t>['수출', '반도체', '네이버 증권']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,90 +2580,90 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>191500</v>
+        <v>12090</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.67%</t>
+          <t>-4.28%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F24" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="H24" t="n">
-        <v>75.98999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>203000</v>
+        <v>12630</v>
       </c>
       <c r="K24" t="n">
-        <v>195000</v>
+        <v>12520</v>
       </c>
       <c r="L24" t="n">
-        <v>195600</v>
+        <v>12930</v>
       </c>
       <c r="M24" t="n">
-        <v>191000</v>
+        <v>12040</v>
       </c>
       <c r="N24" t="n">
-        <v>75.92</v>
+        <v>0.14</v>
       </c>
       <c r="O24" t="n">
-        <v>293655494950</v>
+        <v>32260155990</v>
       </c>
       <c r="P24" t="n">
-        <v>243500</v>
+        <v>20850</v>
       </c>
       <c r="Q24" t="n">
-        <v>58600</v>
+        <v>4020</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>-94000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>기관/외인 매도세 속 주가 하락, 미국 증시 영향 및 네이버 증권 UI 변경 불만.</t>
+          <t>원전 테마의 대장주로 언급되나, 한전기술 등 타 종목으로 수급 쏠림 현상 발생. 거래량 부진 및 계단식 하락 추세로 부정적 전망.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['기관 매도', '외인 매도', '주가 하락']</t>
+          <t>['원전', '수급', '거래량']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>232500</v>
+        <v>233000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-8.10%</t>
+          <t>-7.91%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.96</v>
       </c>
       <c r="E25" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="F25" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G25" t="n">
-        <v>511</v>
+        <v>551</v>
       </c>
       <c r="H25" t="n">
         <v>7.58</v>
@@ -2726,7 +2726,7 @@
         <v>8.539999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>124311998750</v>
+        <v>137051964000</v>
       </c>
       <c r="P25" t="n">
         <v>426000</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>CPI 발표 후 조정 예상 속 공매도 세력의 공격 및 개미 털기 의혹. 반도체 반등 흐름은 유지될 것이라는 전망과 함께 기관 매수세 관찰.</t>
+          <t>공매도 영향 및 기관 매수세 미미로 주가 하락. 반복되는 패턴과 공매도 비중 증가로 부정적 전망이 지배적.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['공매도', 'CPI 발표', '기관 매수']</t>
+          <t>['공매도', '기관', '패턴']</t>
         </is>
       </c>
       <c r="X25" t="n">

--- a/data/trending_integrated_20260911_10.xlsx
+++ b/data/trending_integrated_20260911_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15440</v>
+        <v>16060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+27.71%</t>
+          <t>+29.94%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.11</v>
+        <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>291</v>
+        <v>108</v>
       </c>
       <c r="F2" t="n">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>688</v>
+        <v>81</v>
       </c>
       <c r="H2" t="n">
-        <v>3.14</v>
+        <v>2.39</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12090</v>
+        <v>12360</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>16060</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>12690</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03</v>
+        <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>155533000000</v>
+        <v>204664050465</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="R2" t="n">
-        <v>-347000</v>
+        <v>-139000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 국제 유가 폭등으로 인한 3연상 기대감. WTI 100달러 돌파 및 추가 상승 가능성 언급.</t>
+          <t>젠슨 황의 사이버보안 섹터 지목에 따른 엑스게이트의 급등 및 양자보안 대장으로서의 부각. 매물대 돌파 및 2연상 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['흥구석유', '국제 유가', '중동 전쟁']</t>
+          <t>['젠슨황', '사이버보안', '양자보안']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16060</v>
+        <v>15390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+27.36%</t>
+          <t>+27.30%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.22</v>
+        <v>3.11</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>300</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>176</v>
       </c>
       <c r="G3" t="n">
-        <v>73</v>
+        <v>693</v>
       </c>
       <c r="H3" t="n">
-        <v>2.39</v>
+        <v>3.14</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12610</v>
+        <v>12090</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>0.03</v>
       </c>
       <c r="O3" t="n">
-        <v>198459000000</v>
+        <v>158350000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -711,27 +711,27 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-139000</v>
+        <v>-347000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Nvidia CEO의 사이버 보안 섹터 지목으로 양자 보안 관련주로 부각되며 급등, 향후 추가 상승 기대감이 높음.</t>
+          <t>중동 전쟁 및 국제 유가 폭등으로 인한 3연상 기대감. WTI 100달러 돌파 및 추가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['사이버 보안', '양자 보안', '젠슨 황']</t>
+          <t>['흥구석유', '국제 유가', '중동 전쟁']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,46 +740,46 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>137700</v>
+        <v>8300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+18.40%</t>
+          <t>+26.33%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.26</v>
+        <v>-0.79</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="H4" t="n">
-        <v>4.32</v>
+        <v>2.15</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>116300</v>
+        <v>6570</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.58</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
-        <v>373263000000</v>
+        <v>70429000000</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -803,27 +803,27 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>75000</v>
+        <v>146000</v>
       </c>
       <c r="S4" t="n">
-        <v>87000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>애플 관련주 또는 무라타 제작소와의 연관성으로 상승했으나, 단기 급등 후 차익 실현 매물이 출현함.</t>
+          <t>광통신 및 위성네트워크 섹터 내 우리로의 대장주 역할 부각. 양자주로서의 재료 풍부 및 13,000원 이상의 목표가 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['애플', '무라타 제작소', '손바뀜']</t>
+          <t>['광통신', '양자주', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8300</v>
+        <v>2630</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+23.76%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>541</v>
+        <v>54</v>
       </c>
       <c r="H5" t="n">
-        <v>1.29</v>
+        <v>3.83</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7420</v>
+        <v>2125</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2230</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2692</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="N5" t="n">
-        <v>1.17</v>
+        <v>3.76</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>71924944421</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4810</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="R5" t="n">
-        <v>20000</v>
+        <v>-913000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>임상 시험 디자인 발표 및 기술 수출 가능성 언급. 9월 14일 예정된 데이터 발표에 대한 높은 기대감으로 상승 가능성 부각.</t>
+          <t>젠슨 황의 사이버보안 섹터 지목과 함께 양자컴퓨터 보조금 지원 소식 언급. 드림시큐리티의 대장주로서의 부각 및 상승 신호.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['임상', '기술 수출', '발표']</t>
+          <t>['젠슨황', '사이버보안', '양자컴퓨터']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1930</v>
+        <v>138800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+9.66%</t>
+          <t>+19.97%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.32</v>
+        <v>-0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="H6" t="n">
-        <v>2.44</v>
+        <v>4.32</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1760</v>
+        <v>115700</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>4.58</v>
       </c>
       <c r="O6" t="n">
-        <v>34096000000</v>
+        <v>381915558350</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R6" t="n">
-        <v>-1017000</v>
+        <v>75000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>홍해 사태와 유가 상승 관련주로 부각되며 단기 급등 후 변동성을 보이는 상황.</t>
+          <t>애플 관련주 또는 무라타 제작소와의 연관성으로 상승했으나, 단기 급등 후 차익 실현 매물이 출현함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', '국제 유가', '홍해 사태']</t>
+          <t>['애플', '무라타 제작소', '손바뀜']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28400</v>
+        <v>7680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.81%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>169</v>
+        <v>89</v>
       </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="H7" t="n">
-        <v>0.32</v>
+        <v>11.72</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>26100</v>
+        <v>7100</v>
       </c>
       <c r="K7" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>30300</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.33</v>
+        <v>11.62</v>
       </c>
       <c r="O7" t="n">
-        <v>245462884725</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2000</v>
+        <v>100000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신규 상장 종목으로, 기존 급등주 대비 양호한 흐름을 보이며 수급 개선에 대한 기대감 형성. 3일간 조정 후 상승 가능성 언급.</t>
+          <t>기관의 매수 시그널 및 8000원 돌파 기대감 있으나, 전반적인 지수 하락 및 매도 물량 출회로 부정적 전망. 공매도 관련 언급 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['급등주', '수급', '신규주']</t>
+          <t>['기관', '매수', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9920</v>
+        <v>9910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.90%</t>
+          <t>+6.79%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="H8" t="n">
         <v>4.49</v>
@@ -1162,7 +1162,7 @@
         <v>4.42</v>
       </c>
       <c r="O8" t="n">
-        <v>19305264890</v>
+        <v>19459754245</v>
       </c>
       <c r="P8" t="n">
         <v>15640</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>프리갈리앙 베스트 의료기술상 수상이라는 호재에도 불구하고 주가 하락. 공매도 세력과의 승부 및 역대급 거래량 기대감 언급.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['프리갈리앙 수상', '의료 기술', '공매도']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53100</v>
+        <v>27650</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+2.51%</t>
+          <t>+5.94%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.44</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>177</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="G9" t="n">
-        <v>86</v>
+        <v>310</v>
       </c>
       <c r="H9" t="n">
-        <v>2.92</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>51800</v>
+        <v>26100</v>
       </c>
       <c r="K9" t="n">
-        <v>51300</v>
+        <v>26350</v>
       </c>
       <c r="L9" t="n">
-        <v>53900</v>
+        <v>30300</v>
       </c>
       <c r="M9" t="n">
-        <v>51300</v>
+        <v>25400</v>
       </c>
       <c r="N9" t="n">
-        <v>3.36</v>
+        <v>0.33</v>
       </c>
       <c r="O9" t="n">
-        <v>59744322500</v>
+        <v>256149844325</v>
       </c>
       <c r="P9" t="n">
-        <v>87700</v>
+        <v>39350</v>
       </c>
       <c r="Q9" t="n">
-        <v>17210</v>
+        <v>8200</v>
       </c>
       <c r="R9" t="n">
-        <v>-14000</v>
+        <v>2000</v>
       </c>
       <c r="S9" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 태양광 섹터 흐름 속에서 주가 상승을 기대하나, 개인 매물 출회로 인한 변동성을 겪고 있음.</t>
+          <t>전반적인 하락장 속 스카이랩스의 상대적 강세 및 매수세 유입 언급. 2차 목표가 29,800원 제시 및 3일간 조정 후 수급 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['태양광', '개미 무덤', 'SK']</t>
+          <t>['하락장', '수급', '매수세']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19640</v>
+        <v>53800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>-0.44</v>
       </c>
       <c r="E10" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>331</v>
+        <v>88</v>
       </c>
       <c r="H10" t="n">
-        <v>10.65</v>
+        <v>2.92</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19450</v>
+        <v>53200</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>10.64</v>
+        <v>3.36</v>
       </c>
       <c r="O10" t="n">
-        <v>60909000000</v>
+        <v>63063000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1355,27 +1355,27 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-249000</v>
+        <v>-14000</v>
       </c>
       <c r="S10" t="n">
-        <v>-8000</v>
+        <v>4000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NH투자증권의 목표주가 상향 소식과 함께 '대차해지'를 통한 공매도 세력 대응 요구가 집중됨.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '목표주가 상향']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>416500</v>
+        <v>19570</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>192</v>
+        <v>342</v>
       </c>
       <c r="H11" t="n">
-        <v>38.02</v>
+        <v>10.65</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>415500</v>
+        <v>19450</v>
       </c>
       <c r="K11" t="n">
-        <v>407000</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>417500</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>404000</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>37.82</v>
+        <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>32736847750</v>
+        <v>63146000000</v>
       </c>
       <c r="P11" t="n">
-        <v>822000</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>283000</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>아틀라스 관절부품 전량 수주 및 로봇 사업 확장. 유럽 중국차 관세 반사이익 및 미래차 신기술 공개.</t>
+          <t>대차해지 및 공매도 세력에 대한 경고와 함께 NH투자증권의 목표주가 상향 조정 소식 언급. 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['로봇', '수주', '미래차']</t>
+          <t>['대차해지', '공매도', '목표주가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>90100</v>
+        <v>50700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>159</v>
+        <v>108</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="G12" t="n">
-        <v>680</v>
+        <v>425</v>
       </c>
       <c r="H12" t="n">
-        <v>23.59</v>
+        <v>38.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>89900</v>
+        <v>50400</v>
       </c>
       <c r="K12" t="n">
-        <v>88700</v>
+        <v>50500</v>
       </c>
       <c r="L12" t="n">
-        <v>90400</v>
+        <v>50700</v>
       </c>
       <c r="M12" t="n">
-        <v>88000</v>
+        <v>49650</v>
       </c>
       <c r="N12" t="n">
-        <v>23.65</v>
+        <v>38.69</v>
       </c>
       <c r="O12" t="n">
-        <v>84062168800</v>
+        <v>39154034975</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R12" t="n">
-        <v>-245000</v>
+        <v>-110000</v>
       </c>
       <c r="S12" t="n">
-        <v>10000</v>
+        <v>-4000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 에너지 투자 협상 완료 및 수주 잔고 증가로 인한 기대감 부각. 원전 관련 긍정적 전망 및 목표가 상향 제시.</t>
+          <t>약 4.7조 원 규모의 대규모 수주 공시 확인. 사우디, 베트남 등 겹호재와 외국인 매수세 언급. 긍정적 추세 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['에너지', '수주', '원전']</t>
+          <t>['수주', '공시', '외국인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3620</v>
+        <v>1912</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="E13" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="H13" t="n">
-        <v>0.73</v>
+        <v>2.44</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3620</v>
+        <v>1901</v>
       </c>
       <c r="K13" t="n">
-        <v>3725</v>
+        <v>2050</v>
       </c>
       <c r="L13" t="n">
-        <v>3915</v>
+        <v>2080</v>
       </c>
       <c r="M13" t="n">
-        <v>3550</v>
+        <v>1911</v>
       </c>
       <c r="N13" t="n">
-        <v>1.54</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>34467093988</v>
+        <v>35635359214</v>
       </c>
       <c r="P13" t="n">
-        <v>4335</v>
+        <v>4795</v>
       </c>
       <c r="Q13" t="n">
-        <v>1246</v>
+        <v>1524</v>
       </c>
       <c r="R13" t="n">
-        <v>214000</v>
+        <v>-1017000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>홍해 사태 및 국제 유가 상승 우려에 따른 전쟁 테마주로서의 흥아해운 및 장금상선 언급. 일부 부정적 전망과 함께 단기 매매 의견 제시.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['국제유가', '홍해', '전쟁테마주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50300</v>
+        <v>417000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="E14" t="n">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="F14" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>417</v>
+        <v>194</v>
       </c>
       <c r="H14" t="n">
-        <v>38.78</v>
+        <v>38.02</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>50400</v>
+        <v>415500</v>
       </c>
       <c r="K14" t="n">
-        <v>50500</v>
+        <v>407000</v>
       </c>
       <c r="L14" t="n">
-        <v>50600</v>
+        <v>417500</v>
       </c>
       <c r="M14" t="n">
-        <v>49650</v>
+        <v>404000</v>
       </c>
       <c r="N14" t="n">
-        <v>38.69</v>
+        <v>37.82</v>
       </c>
       <c r="O14" t="n">
-        <v>37145675825</v>
+        <v>34485095750</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>822000</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>283000</v>
       </c>
       <c r="R14" t="n">
-        <v>-110000</v>
+        <v>5000</v>
       </c>
       <c r="S14" t="n">
-        <v>-4000</v>
+        <v>1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>약 4.7조 원 규모의 대규모 수주 공시 확인. 사우디, 베트남 등 겹호재와 외국인 매수세 언급. 긍정적 추세 전망.</t>
+          <t>현대모비스, 아틀라스 관절 부품 전량 수주 및 그룹사 양산 로드맵 가동. 유럽 및 중국차 관세 부과 관련 호재 기대. 미래차 및 로봇 신기술 60종 공개.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수주', '공시', '외국인']</t>
+          <t>['로봇', '관절 부품', '미래차']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14930</v>
+        <v>90100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>163</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="G15" t="n">
-        <v>189</v>
+        <v>686</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>23.59</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>15040</v>
+        <v>89900</v>
       </c>
       <c r="K15" t="n">
-        <v>14550</v>
+        <v>88700</v>
       </c>
       <c r="L15" t="n">
-        <v>15260</v>
+        <v>90400</v>
       </c>
       <c r="M15" t="n">
-        <v>14350</v>
+        <v>88000</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="O15" t="n">
-        <v>14291853775</v>
+        <v>88171384700</v>
       </c>
       <c r="P15" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>23000</v>
+        <v>-245000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 부지 확보 및 메가 건설 관련 긍정적 뉴스 부각. 친환경 투자 및 건설 사업 확장으로 인한 상승 기대감 형성.</t>
+          <t>미국 에너지 투자 협상 완료 및 수주 잔고 증가로 인한 기대감 부각. 원전 관련 긍정적 전망 및 목표가 상향 제시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체', '건설', '호남']</t>
+          <t>['에너지', '수주', '원전']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8800</v>
+        <v>3600</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.90%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.03</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="H16" t="n">
-        <v>27.19</v>
+        <v>0.73</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8970</v>
+        <v>3620</v>
       </c>
       <c r="K16" t="n">
-        <v>8780</v>
+        <v>3725</v>
       </c>
       <c r="L16" t="n">
-        <v>8870</v>
+        <v>3915</v>
       </c>
       <c r="M16" t="n">
-        <v>8680</v>
+        <v>3550</v>
       </c>
       <c r="N16" t="n">
-        <v>27.16</v>
+        <v>1.54</v>
       </c>
       <c r="O16" t="n">
-        <v>8982521055</v>
+        <v>35274537555</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>4335</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>1246</v>
       </c>
       <c r="R16" t="n">
-        <v>-28000</v>
+        <v>214000</v>
       </c>
       <c r="S16" t="n">
-        <v>-33000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 강한 불만과 함께 회사의 실적 부진 및 저평가에 대한 부정적인 인식이 지배적임.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['저평가', '실적 부진', '금리 인상']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>192400</v>
+        <v>8790</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="H17" t="n">
-        <v>75.98999999999999</v>
+        <v>27.19</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>197500</v>
+        <v>8970</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>8780</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>8870</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>8680</v>
       </c>
       <c r="N17" t="n">
-        <v>75.92</v>
+        <v>27.16</v>
       </c>
       <c r="O17" t="n">
-        <v>303479000000</v>
+        <v>9628402775</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>17950</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>8120</v>
       </c>
       <c r="R17" t="n">
-        <v>-405000</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-52000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
+          <t>주가 상승에 대한 강한 불만과 함께 회사의 실적 부진 및 저평가에 대한 부정적인 인식이 지배적임.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['우선주', '기관 매도', '미국 증시']</t>
+          <t>['저평가', '실적 부진', '금리 인상']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14110</v>
+        <v>14340</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.36%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.11</v>
+        <v>-0.39</v>
       </c>
       <c r="E18" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G18" t="n">
-        <v>385</v>
+        <v>149</v>
       </c>
       <c r="H18" t="n">
-        <v>5.98</v>
+        <v>2.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14600</v>
+        <v>14740</v>
       </c>
       <c r="K18" t="n">
-        <v>14800</v>
+        <v>14050</v>
       </c>
       <c r="L18" t="n">
-        <v>14950</v>
+        <v>14450</v>
       </c>
       <c r="M18" t="n">
-        <v>14020</v>
+        <v>14030</v>
       </c>
       <c r="N18" t="n">
-        <v>6.09</v>
+        <v>2.89</v>
       </c>
       <c r="O18" t="n">
-        <v>65394130630</v>
+        <v>30794146780</v>
       </c>
       <c r="P18" t="n">
-        <v>30200</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>3540</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-297000</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-61000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>원전 관련 테마 기대감 속에서 모건 스탠리의 대량 매수 관측. 단기 과열 우려도 있으나, 원전주의 강력한 재료 기반 상승 가능성 언급.</t>
+          <t>외국인 매수세 및 프로그램 매수에 따른 상승 기대감 존재. 단기적인 상승 움직임 예측되나, 전반적인 증시 하락 분위기 속에 관망세 짙음.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전 테마', '모건 스탠리', '수주']</t>
+          <t>['외국인', '매수', '움직임']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14230</v>
+        <v>191600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.39</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G19" t="n">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14740</v>
+        <v>197500</v>
       </c>
       <c r="K19" t="n">
-        <v>14050</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>14450</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>14030</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.89</v>
+        <v>75.92</v>
       </c>
       <c r="O19" t="n">
-        <v>28632174220</v>
+        <v>317111000000</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-34000</v>
+        <v>-405000</v>
       </c>
       <c r="S19" t="n">
-        <v>-1000</v>
+        <v>-52000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>외국인 매수세 및 프로그램 매수에 따른 상승 기대감 존재. 단기적인 상승 움직임 예측되나, 전반적인 증시 하락 분위기 속에 관망세 짙음.</t>
+          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['외국인', '매수', '움직임']</t>
+          <t>['우선주', '기관 매도', '미국 증시']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7410</v>
+        <v>14120</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>261</v>
+        <v>391</v>
       </c>
       <c r="H20" t="n">
-        <v>11.72</v>
+        <v>5.98</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7680</v>
+        <v>14600</v>
       </c>
       <c r="K20" t="n">
-        <v>7540</v>
+        <v>14800</v>
       </c>
       <c r="L20" t="n">
-        <v>7660</v>
+        <v>14950</v>
       </c>
       <c r="M20" t="n">
-        <v>7390</v>
+        <v>14020</v>
       </c>
       <c r="N20" t="n">
-        <v>11.62</v>
+        <v>6.09</v>
       </c>
       <c r="O20" t="n">
-        <v>6952711385</v>
+        <v>69435550625</v>
       </c>
       <c r="P20" t="n">
-        <v>8850</v>
+        <v>30200</v>
       </c>
       <c r="Q20" t="n">
-        <v>4220</v>
+        <v>3540</v>
       </c>
       <c r="R20" t="n">
-        <v>100000</v>
+        <v>-297000</v>
       </c>
       <c r="S20" t="n">
-        <v>-1000</v>
+        <v>-61000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>기관의 매수 시그널 및 8000원 돌파 기대감 있으나, 전반적인 지수 하락 및 매도 물량 출회로 부정적 전망. 공매도 관련 언급 존재.</t>
+          <t>원전 관련 테마 기대감 속에서 모건 스탠리의 대량 매수 관측. 단기 과열 우려도 있으나, 원전주의 강력한 재료 기반 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['기관', '매수', '공매도']</t>
+          <t>['원전 테마', '모건 스탠리', '수주']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -2326,13 +2326,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H21" t="n">
         <v>25.55</v>
@@ -2358,7 +2358,7 @@
         <v>24.99</v>
       </c>
       <c r="O21" t="n">
-        <v>29471000000</v>
+        <v>30526000000</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1782000</v>
+        <v>1783000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.99%</t>
+          <t>-3.78%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="G22" t="n">
-        <v>1141</v>
+        <v>1183</v>
       </c>
       <c r="H22" t="n">
         <v>50.55</v>
@@ -2435,28 +2435,28 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1856000</v>
+        <v>1853000</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1773000</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1795000</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1768000</v>
       </c>
       <c r="N22" t="n">
         <v>50.67</v>
       </c>
       <c r="O22" t="n">
-        <v>1868848000000</v>
+        <v>1946826620000</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>305500</v>
       </c>
       <c r="R22" t="n">
         <v>-166000</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>AI 클라우드 수요 증가 소식에도 불구하고 주가는 하락세를 보이며, 네이버 증권 인터페이스 변경에 대한 불만이 제기됨.</t>
+          <t>오라클의 AI 클라우드 수요 급증 호실적 발표에도 불구하고 SK하이닉스 주가 하락에 대한 우려. 네이버 증권 UI 변경에 대한 불만.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['AI', '반도체 수출', '네이버 증권']</t>
+          <t>['AI', '반도체', '주가하락']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2495,70 +2495,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>258250</v>
+        <v>12150</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.00%</t>
+          <t>-3.80%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="E23" t="n">
-        <v>800</v>
+        <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>495</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>1841</v>
+        <v>56</v>
       </c>
       <c r="H23" t="n">
-        <v>46.71</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>269000</v>
+        <v>12630</v>
       </c>
       <c r="K23" t="n">
-        <v>258000</v>
+        <v>12520</v>
       </c>
       <c r="L23" t="n">
-        <v>261000</v>
+        <v>12930</v>
       </c>
       <c r="M23" t="n">
-        <v>257500</v>
+        <v>12010</v>
       </c>
       <c r="N23" t="n">
-        <v>46.81</v>
+        <v>0.14</v>
       </c>
       <c r="O23" t="n">
-        <v>1252671497250</v>
+        <v>33012073510</v>
       </c>
       <c r="P23" t="n">
-        <v>374500</v>
+        <v>20850</v>
       </c>
       <c r="Q23" t="n">
-        <v>72100</v>
+        <v>4020</v>
       </c>
       <c r="R23" t="n">
-        <v>-615000</v>
+        <v>-94000</v>
       </c>
       <c r="S23" t="n">
-        <v>-530000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>수출 호조에도 불구하고 주가는 부진하며, 네이버 증권 게시판 개편에 대한 불만이 제기됨.</t>
+          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['수출', '반도체', '네이버 증권']</t>
+          <t>['원전', '테마주', '거래량']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>104</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,90 +2580,90 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12090</v>
+        <v>15040</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-4.28%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G24" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>12630</v>
+        <v>15640</v>
       </c>
       <c r="K24" t="n">
-        <v>12520</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>12930</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>12040</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>32260155990</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>20850</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4020</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>-94000</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>원전 테마의 대장주로 언급되나, 한전기술 등 타 종목으로 수급 쏠림 현상 발생. 거래량 부진 및 계단식 하락 추세로 부정적 전망.</t>
+          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['원전', '수급', '거래량']</t>
+          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,38 +2672,38 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>233000</v>
+        <v>257750</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-7.91%</t>
+          <t>-4.18%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.96</v>
+        <v>-0.1</v>
       </c>
       <c r="E25" t="n">
-        <v>161</v>
+        <v>800</v>
       </c>
       <c r="F25" t="n">
-        <v>86</v>
+        <v>501</v>
       </c>
       <c r="G25" t="n">
-        <v>551</v>
+        <v>1782</v>
       </c>
       <c r="H25" t="n">
-        <v>7.58</v>
+        <v>46.71</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,58 +2711,242 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>253000</v>
+        <v>269000</v>
       </c>
       <c r="K25" t="n">
-        <v>241000</v>
+        <v>258000</v>
       </c>
       <c r="L25" t="n">
-        <v>241000</v>
+        <v>261000</v>
       </c>
       <c r="M25" t="n">
-        <v>231000</v>
+        <v>257500</v>
       </c>
       <c r="N25" t="n">
-        <v>8.539999999999999</v>
+        <v>46.81</v>
       </c>
       <c r="O25" t="n">
-        <v>137051964000</v>
+        <v>1356287133000</v>
       </c>
       <c r="P25" t="n">
-        <v>426000</v>
+        <v>374500</v>
       </c>
       <c r="Q25" t="n">
-        <v>86100</v>
+        <v>72100</v>
       </c>
       <c r="R25" t="n">
-        <v>-224000</v>
+        <v>-615000</v>
       </c>
       <c r="S25" t="n">
-        <v>-14000</v>
+        <v>-530000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>공매도 영향 및 기관 매수세 미미로 주가 하락. 반복되는 패턴과 공매도 비중 증가로 부정적 전망이 지배적.</t>
+          <t>수출 부진 및 네이버 증권 게시판 변경에 대한 불만 제기. 반도체 수출 역대 최대에도 주가 하락에 대한 비판.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['공매도', '기관', '패턴']</t>
+          <t>['수출', '반도체', '주가하락']</t>
         </is>
       </c>
       <c r="X25" t="n">
+        <v>104</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>페니트리움바이오</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7800</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>-6.02%</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E26" t="n">
+        <v>125</v>
+      </c>
+      <c r="F26" t="n">
+        <v>60</v>
+      </c>
+      <c r="G26" t="n">
+        <v>556</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>8300</v>
+      </c>
+      <c r="K26" t="n">
+        <v>8400</v>
+      </c>
+      <c r="L26" t="n">
+        <v>8700</v>
+      </c>
+      <c r="M26" t="n">
+        <v>7720</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O26" t="n">
+        <v>13132671425</v>
+      </c>
+      <c r="P26" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2300</v>
+      </c>
+      <c r="R26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>페니트리움바이오, 9월 14일 WCLC 센딥파텔 교수 데이터 발표 예정. 기술 수출 기대감 및 제약 회사 급등 흐름 속에서 주목.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>['임상', '데이터 발표', '기술 수출']</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>187660</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>232500</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-8.10%</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="E27" t="n">
+        <v>164</v>
+      </c>
+      <c r="F27" t="n">
+        <v>87</v>
+      </c>
+      <c r="G27" t="n">
+        <v>567</v>
+      </c>
+      <c r="H27" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>253000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>241000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>241000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>231000</v>
+      </c>
+      <c r="N27" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="O27" t="n">
+        <v>139519702750</v>
+      </c>
+      <c r="P27" t="n">
+        <v>426000</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>86100</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-224000</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-14000</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>한미반도체, 공매도 물량 급증으로 인한 주가 하락세. 기관의 소량 매수세 관찰되나 전반적인 매도 압력 우세.</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>['공매도', '주가 하락', '기관 매수']</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
         <v>1</v>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>042700</t>
         </is>
